--- a/changes/54r-ammo-super.xlsx
+++ b/changes/54r-ammo-super.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="102">
   <si>
     <t>7.62x54R ammo scoring model</t>
   </si>
@@ -75,6 +75,9 @@
     <t>Value</t>
   </si>
   <si>
+    <t>balancing.csv inputs</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -87,6 +90,9 @@
     <t>Damage reference</t>
   </si>
   <si>
+    <t>calibers.csv damage inputs</t>
+  </si>
+  <si>
     <t>weighted damage scores above/below this</t>
   </si>
   <si>
@@ -105,18 +111,30 @@
     <t>Penetration reference</t>
   </si>
   <si>
+    <t>calculated torso damage by range</t>
+  </si>
+  <si>
     <t>Damage distance weights</t>
   </si>
   <si>
+    <t>calibers.csv traits &amp; penetration inputs</t>
+  </si>
+  <si>
     <t>Distance (studs)</t>
   </si>
   <si>
     <t>Weight</t>
   </si>
   <si>
+    <t>penetration model</t>
+  </si>
+  <si>
     <t>Rationale</t>
   </si>
   <si>
+    <t>weighted score</t>
+  </si>
+  <si>
     <t>close</t>
   </si>
   <si>
@@ -129,6 +147,9 @@
     <t>long</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>very long</t>
   </si>
   <si>
@@ -138,292 +159,217 @@
     <t>Weight check</t>
   </si>
   <si>
-    <t>balancing.csv inputs</t>
+    <t>pretty_name</t>
+  </si>
+  <si>
+    <t>ergonomics</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>horizontal_recoil</t>
+  </si>
+  <si>
+    <t>vertical_recoil</t>
+  </si>
+  <si>
+    <t>barrel_deviation</t>
+  </si>
+  <si>
+    <t>bullet_damage</t>
+  </si>
+  <si>
+    <t>bullet_velocity</t>
+  </si>
+  <si>
+    <t>fire_rate</t>
+  </si>
+  <si>
+    <t>muzzle_loudness</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>damage_torso_a</t>
+  </si>
+  <si>
+    <t>damage_torso_b</t>
+  </si>
+  <si>
+    <t>damage_torso_c</t>
+  </si>
+  <si>
+    <t>damage_torso_d</t>
+  </si>
+  <si>
+    <t>damage_arm_d</t>
+  </si>
+  <si>
+    <t>damage_leg_d</t>
+  </si>
+  <si>
+    <t>damage_head_d</t>
+  </si>
+  <si>
+    <t>damage_25</t>
+  </si>
+  <si>
+    <t>damage_75</t>
+  </si>
+  <si>
+    <t>damage_150</t>
+  </si>
+  <si>
+    <t>damage_250</t>
+  </si>
+  <si>
+    <t>damage_375</t>
+  </si>
+  <si>
+    <t>damage_525</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>weighted_damage</t>
+  </si>
+  <si>
+    <t>velocity_drop</t>
+  </si>
+  <si>
+    <t>suppression</t>
+  </si>
+  <si>
+    <t>bullet_penetration_ability</t>
+  </si>
+  <si>
+    <t>pen_low</t>
+  </si>
+  <si>
+    <t>pen_high</t>
+  </si>
+  <si>
+    <t>pen_velocity_low</t>
+  </si>
+  <si>
+    <t>pen_velocity_high</t>
+  </si>
+  <si>
+    <t>effective_velocity</t>
   </si>
   <si>
     <t>balancing.csv stat weights</t>
   </si>
   <si>
+    <t>penetration</t>
+  </si>
+  <si>
+    <t>balance_score</t>
+  </si>
+  <si>
+    <t>damage_score</t>
+  </si>
+  <si>
+    <t>velocity_drop_score</t>
+  </si>
+  <si>
+    <t>suppression_score</t>
+  </si>
+  <si>
+    <t>penetration_score</t>
+  </si>
+  <si>
+    <t>strength</t>
+  </si>
+  <si>
     <t>Stat</t>
   </si>
   <si>
+    <t>7.62x54r_pga_rifle_150gr_spbt</t>
+  </si>
+  <si>
     <t>Interpretation</t>
   </si>
   <si>
-    <t>ergonomics</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>horizontal_recoil</t>
-  </si>
-  <si>
-    <t>calibers.csv damage inputs</t>
-  </si>
-  <si>
-    <t>vertical_recoil</t>
-  </si>
-  <si>
-    <t>barrel_deviation</t>
-  </si>
-  <si>
-    <t>bullet_damage</t>
+    <t>Prva Garda Rifle Line 150gr SP-BT</t>
   </si>
   <si>
     <t>fractional modifier</t>
   </si>
   <si>
-    <t>bullet_velocity</t>
-  </si>
-  <si>
-    <t>calculated torso damage by range</t>
-  </si>
-  <si>
-    <t>fire_rate</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
     <t>excluded from performance strength</t>
   </si>
   <si>
     <t>muzzle loudness</t>
   </si>
   <si>
-    <t>calibers.csv traits &amp; penetration inputs</t>
-  </si>
-  <si>
     <t>fractional modifier, lower = better</t>
   </si>
   <si>
     <t>Ammo-specific metric weights</t>
   </si>
   <si>
-    <t>weighted_damage</t>
-  </si>
-  <si>
-    <t>penetration model</t>
-  </si>
-  <si>
     <t>points per damage above reference</t>
   </si>
   <si>
-    <t>velocity_drop</t>
-  </si>
-  <si>
-    <t>weighted score</t>
-  </si>
-  <si>
     <t>small effect; lower is better</t>
   </si>
   <si>
-    <t>suppression</t>
-  </si>
-  <si>
     <t>moderate effect; higher is better</t>
   </si>
   <si>
-    <t>penetration</t>
-  </si>
-  <si>
     <t>noticable effect; higher is better</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>pretty_name</t>
-  </si>
-  <si>
-    <t>muzzle_loudness</t>
-  </si>
-  <si>
-    <t>damage_torso_a</t>
-  </si>
-  <si>
-    <t>damage_torso_b</t>
-  </si>
-  <si>
-    <t>damage_torso_c</t>
-  </si>
-  <si>
-    <t>damage_torso_d</t>
-  </si>
-  <si>
-    <t>damage_arm_d</t>
-  </si>
-  <si>
-    <t>damage_leg_d</t>
-  </si>
-  <si>
-    <t>damage_head_d</t>
-  </si>
-  <si>
-    <t>damage_25</t>
-  </si>
-  <si>
-    <t>damage_75</t>
-  </si>
-  <si>
-    <t>damage_150</t>
-  </si>
-  <si>
-    <t>damage_250</t>
-  </si>
-  <si>
-    <t>damage_375</t>
-  </si>
-  <si>
-    <t>damage_525</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>bullet_penetration_ability</t>
-  </si>
-  <si>
-    <t>pen_low</t>
-  </si>
-  <si>
-    <t>pen_high</t>
-  </si>
-  <si>
-    <t>pen_velocity_low</t>
-  </si>
-  <si>
-    <t>pen_velocity_high</t>
-  </si>
-  <si>
-    <t>effective_velocity</t>
-  </si>
-  <si>
-    <t>balance_score</t>
-  </si>
-  <si>
-    <t>damage_score</t>
-  </si>
-  <si>
-    <t>velocity_drop_score</t>
-  </si>
-  <si>
-    <t>suppression_score</t>
-  </si>
-  <si>
-    <t>penetration_score</t>
-  </si>
-  <si>
-    <t>strength</t>
-  </si>
-  <si>
-    <t>7.62x54r_zim_rifle_150gr_spbt</t>
-  </si>
-  <si>
-    <t>ZiM Rifle Line 150gr SPBT</t>
-  </si>
-  <si>
     <t>7.62x54r_norilsk_7n1_151gr_ps</t>
   </si>
   <si>
-    <t>7N1</t>
-  </si>
-  <si>
-    <t>7.62x54r_norilsk_7t2_149gr_green_tracer</t>
-  </si>
-  <si>
-    <t>7T2M</t>
-  </si>
-  <si>
-    <t>57-N-323S</t>
-  </si>
-  <si>
-    <t>57-N-323S 148gr</t>
-  </si>
-  <si>
-    <t>Sellier &amp; Bellot 174g HPBT</t>
-  </si>
-  <si>
-    <t>Sellier &amp; Bellot 174gr HPBT</t>
-  </si>
-  <si>
-    <t>7N14 (AP SNIPER)</t>
-  </si>
-  <si>
-    <t>7N14</t>
-  </si>
-  <si>
-    <t>7N37 Tungsten Carbide (AP SNIPER BUT MORE)</t>
-  </si>
-  <si>
-    <t>7N37 182gr AP</t>
-  </si>
-  <si>
-    <t>B-32M (API LMFAO)</t>
-  </si>
-  <si>
-    <t>B-32M 155gr AP Incendiary</t>
-  </si>
-  <si>
-    <t>✅</t>
-  </si>
-  <si>
-    <t>7.62x51 For Reference</t>
-  </si>
-  <si>
-    <t>7.62x51_appalachian_m80_149gr_fmj</t>
-  </si>
-  <si>
-    <t>Appalachian M80 149gr FMJ</t>
-  </si>
-  <si>
-    <t>7.62x51_appalachian_m62_142gr_red_tracer</t>
-  </si>
-  <si>
-    <t>Appalachian M62 142gr Red Tracer</t>
-  </si>
-  <si>
-    <t>7.82x51_laccio_308app_extrema_leadless_168gr_tipped_tsx_bt</t>
-  </si>
-  <si>
-    <t>Laccio .308 Appalachian Extrema Leadless 168gr Tipped TSX-BT</t>
-  </si>
-  <si>
-    <t>7.62x51_federal_m118lr_175gr_otm</t>
-  </si>
-  <si>
-    <t>Federal M118LR 175gr OTM</t>
-  </si>
-  <si>
-    <t>7.62x51_cae_l59a1_155gr_enhanced_performance</t>
-  </si>
-  <si>
-    <t>CAe L59A1 155gr Enhanced Performance</t>
-  </si>
-  <si>
-    <t>7.62x51_appalachian_m80a1_130gr_epr</t>
-  </si>
-  <si>
-    <t>Appalachian M80A1 130gr EPR</t>
-  </si>
-  <si>
-    <t>7.62x51_emmeo_m993_129gr_ap</t>
-  </si>
-  <si>
-    <t>Emmeo M993 129gr AP</t>
-  </si>
-  <si>
-    <t>7.62x51_federal_gold_medal_168gr_hpbt</t>
-  </si>
-  <si>
-    <t>MK319</t>
-  </si>
-  <si>
-    <t>7.62x51_hawthorne_sub_x_200gr_subsonic</t>
-  </si>
-  <si>
-    <t>Hawthorne Sub X 200gr Subsonic</t>
+    <t>Norilsk 7N1 Snaiperskye 151gr PS</t>
+  </si>
+  <si>
+    <t>7.62x54r_norilsk_7t2m_149gr_green_tracer</t>
+  </si>
+  <si>
+    <t>Norilsk 7T2M 149gr Green Tracer</t>
+  </si>
+  <si>
+    <t>7.62x54r_tsniitekhmash_57_n_323s_148gr_lps</t>
+  </si>
+  <si>
+    <t>TsNIITekhMash 57-N-323S 148gr LPS</t>
+  </si>
+  <si>
+    <t>7.62x54r_s&amp;b_174gr_hpbt</t>
+  </si>
+  <si>
+    <t>Serrano &amp; Belmonte 174gr HPBT</t>
+  </si>
+  <si>
+    <t>7.62x54r_norilsk_7n14_152gr_snb</t>
+  </si>
+  <si>
+    <t>Norilsk 7N14 Snaiperskaya 152gr SNB</t>
+  </si>
+  <si>
+    <t>7.62x54r_tsniitekhmash_7n37_182gr_bs</t>
+  </si>
+  <si>
+    <t>TsNIITekhMash 7N37 Chórnoye Górlyshko 182gr BS</t>
+  </si>
+  <si>
+    <t>7.62x54r_norilsk_b32m_164gr_api</t>
+  </si>
+  <si>
+    <t>Norilsk B-32M 162gr API</t>
+  </si>
+  <si>
+    <t>7.62x54r_subsonic_200gr</t>
+  </si>
+  <si>
+    <t>Tezu Handloaded 200gr Subsonic</t>
   </si>
 </sst>
 </file>
@@ -468,14 +414,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FF1F2933"/>
+      <b/>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF1F2933"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
@@ -549,18 +495,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF684A86"/>
-        <bgColor rgb="FF684A86"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7F9"/>
-        <bgColor rgb="FFF5F7F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF385B47"/>
         <bgColor rgb="FF385B47"/>
       </patternFill>
@@ -573,14 +507,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1ECF7"/>
-        <bgColor rgb="FFF1ECF7"/>
+        <fgColor rgb="FF684A86"/>
+        <bgColor rgb="FF684A86"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2C6E73"/>
         <bgColor rgb="FF2C6E73"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7F9"/>
+        <bgColor rgb="FFF5F7F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -593,6 +533,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF7EE"/>
         <bgColor rgb="FFEDF7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1ECF7"/>
+        <bgColor rgb="FFF1ECF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -652,6 +598,12 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
       <top style="thin">
         <color rgb="FFD8E0E7"/>
       </top>
@@ -671,8 +623,9 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color rgb="FFD8E0E7"/>
+      </top>
     </border>
     <border>
       <left/>
@@ -682,18 +635,11 @@
       </top>
       <bottom/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD8E0E7"/>
-      </top>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -711,67 +657,115 @@
     <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="6" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="4" fontId="7" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="6" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="4" fontId="7" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="8" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="9" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="9" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="10" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="4" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="9" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="11" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -779,182 +773,131 @@
     <xf borderId="6" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="12" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="12" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="10" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="12" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="10" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="10" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="10" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="11" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="12" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="13" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="10" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="10" fillId="11" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="10" fillId="10" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="10" fillId="11" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="10" fillId="12" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="12" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="12" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="12" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="11" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="12" numFmtId="3" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="14" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="4" fontId="10" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="4" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="11" fillId="11" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="13" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="11" fillId="4" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="11" fillId="4" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="11" fillId="11" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="11" fillId="12" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="11" fillId="11" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="11" fillId="12" fontId="10" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="11" fillId="9" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="12" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="12" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="12" numFmtId="3" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="12" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="11" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1014,120 +957,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4876800" cy="3771900"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4876800" cy="3771900"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4876800" cy="3771900"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4876800" cy="3762375"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1449,8 +1279,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>24</v>
+      <c r="A1" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1463,17 +1293,17 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="25" t="s">
-        <v>31</v>
+      <c r="M1" s="13" t="s">
+        <v>8</v>
       </c>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="28" t="s">
-        <v>37</v>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
@@ -1482,8 +1312,8 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="3"/>
-      <c r="AB1" s="25" t="s">
-        <v>42</v>
+      <c r="AB1" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
@@ -1491,12 +1321,12 @@
       <c r="AF1" s="2"/>
       <c r="AG1" s="2"/>
       <c r="AH1" s="3"/>
-      <c r="AI1" s="32" t="s">
-        <v>46</v>
+      <c r="AI1" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="AJ1" s="3"/>
-      <c r="AK1" s="35" t="s">
-        <v>49</v>
+      <c r="AK1" s="24" t="s">
+        <v>22</v>
       </c>
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
@@ -1505,216 +1335,216 @@
       <c r="AP1" s="3"/>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="U2" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="X2" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y2" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="AA2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="40" t="s">
+      <c r="AB2" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="L2" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="39" t="s">
+      <c r="AC2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="AD2" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="AE2" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="39" t="s">
+      <c r="AF2" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="AG2" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="R2" s="39" t="s">
+      <c r="AH2" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="S2" s="39" t="s">
+      <c r="AI2" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="T2" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="U2" s="39" t="s">
+      <c r="AJ2" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="V2" s="39" t="s">
+      <c r="AK2" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="W2" s="39" t="s">
+      <c r="AL2" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="X2" s="39" t="s">
+      <c r="AM2" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="AN2" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" s="40" t="s">
+      <c r="AO2" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB2" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC2" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD2" s="39" t="s">
+      <c r="AP2" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="AE2" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF2" s="39" t="s">
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="AG2" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH2" s="39" t="s">
+      <c r="B3" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="AI2" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ2" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK2" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL2" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM2" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN2" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO2" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP2" s="39" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="43">
+      <c r="C3" s="32">
         <v>1.0</v>
       </c>
-      <c r="D3" s="44">
+      <c r="D3" s="33">
         <v>0.0</v>
       </c>
-      <c r="E3" s="43">
+      <c r="E3" s="32">
         <v>0.0</v>
       </c>
-      <c r="F3" s="43">
+      <c r="F3" s="32">
         <v>-2.0</v>
       </c>
-      <c r="G3" s="44">
+      <c r="G3" s="33">
         <v>-0.05</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="43">
+      <c r="H3" s="35"/>
+      <c r="I3" s="32">
         <v>-100.0</v>
       </c>
-      <c r="J3" s="46"/>
-      <c r="K3" s="47">
+      <c r="J3" s="36"/>
+      <c r="K3" s="37">
         <v>0.0</v>
       </c>
-      <c r="L3" s="48">
+      <c r="L3" s="38">
         <v>1000.0</v>
       </c>
-      <c r="M3" s="49">
+      <c r="M3" s="40">
         <v>-0.042</v>
       </c>
-      <c r="N3" s="49">
+      <c r="N3" s="40">
         <v>120.0</v>
       </c>
-      <c r="O3" s="49">
+      <c r="O3" s="40">
         <v>121.0</v>
       </c>
-      <c r="P3" s="49">
+      <c r="P3" s="40">
         <v>1.0</v>
       </c>
-      <c r="Q3" s="49">
+      <c r="Q3" s="40">
         <v>0.35</v>
       </c>
-      <c r="R3" s="50">
+      <c r="R3" s="41">
         <v>0.55</v>
       </c>
-      <c r="S3" s="51">
+      <c r="S3" s="42">
         <v>2.5</v>
       </c>
-      <c r="T3" s="52">
+      <c r="T3" s="44">
         <f>MAX(MIN($M3*Model!$A$13+$N3,$O3)*$P3,0)</f>
         <v>117.9</v>
       </c>
-      <c r="U3" s="52">
+      <c r="U3" s="44">
         <f>MAX(MIN($M3*Model!$A$14+$N3,$O3)*$P3,0)</f>
         <v>115.8</v>
       </c>
-      <c r="V3" s="52">
+      <c r="V3" s="44">
         <f>MAX(MIN($M3*Model!$A$15+$N3,$O3)*$P3,0)</f>
         <v>111.6</v>
       </c>
-      <c r="W3" s="52">
+      <c r="W3" s="44">
         <f>MAX(MIN($M3*Model!$A$16+$N3,$O3)*$P3,0)</f>
         <v>107.4</v>
       </c>
-      <c r="X3" s="52">
+      <c r="X3" s="44">
         <f>MAX(MIN($M3*Model!$A$17+$N3,$O3)*$P3,0)</f>
         <v>103.2</v>
       </c>
-      <c r="Y3" s="52">
+      <c r="Y3" s="44">
         <f>MAX(MIN($M3*Model!$A$18+$N3,$O3)*$P3,0)</f>
         <v>96.9</v>
       </c>
-      <c r="Z3" s="52">
+      <c r="Z3" s="44">
         <f>MAX(MIN($M3*Model!$A$19+$N3,$O3)*$P3,0)</f>
         <v>88.5</v>
       </c>
-      <c r="AA3" s="52">
+      <c r="AA3" s="44">
         <f>T3*Model!$B$13+U3*Model!$B$14+V3*Model!$B$15+W3*Model!$B$16+X3*Model!$B$17+Y3*Model!$B$18+Z3*Model!$B$19</f>
         <v>107.715</v>
       </c>
@@ -1724,7 +1554,7 @@
       <c r="AC3" s="53">
         <v>0.8</v>
       </c>
-      <c r="AD3" s="51" t="str">
+      <c r="AD3" s="42" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE3,";",'7.62x54R-ammo'!$AF3,";",'7.62x54R-ammo'!$AG3,";",'7.62x54R-ammo'!$AH3,")")</f>
         <v>stat(bullet_velocity;0;0.5;1500;3000)</v>
       </c>
@@ -1744,8 +1574,8 @@
         <f>Model!$B$4+IF(I3="",0,I3)</f>
         <v>2019</v>
       </c>
-      <c r="AJ3" s="52">
-        <f t="shared" ref="AJ3:AJ10" si="1">MAX(AE3,MIN(AF3,AE3+(AI3-AG3)*(AF3-AE3)/(AH3-AG3)))</f>
+      <c r="AJ3" s="44">
+        <f t="shared" ref="AJ3:AJ11" si="1">MAX(AE3,MIN(AF3,AE3+(AI3-AG3)*(AF3-AE3)/(AH3-AG3)))</f>
         <v>0.173</v>
       </c>
       <c r="AK3" s="57">
@@ -1769,93 +1599,93 @@
         <v>-4.962</v>
       </c>
       <c r="AP3" s="57">
-        <f t="shared" ref="AP3:AP10" si="2">SUM(AK3:AO3)</f>
+        <f t="shared" ref="AP3:AP11" si="2">SUM(AK3:AO3)</f>
         <v>1.5455</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="32">
         <v>-1.0</v>
       </c>
-      <c r="D4" s="44">
+      <c r="D4" s="33">
         <v>0.01</v>
       </c>
-      <c r="E4" s="43">
+      <c r="E4" s="32">
         <v>1.0</v>
       </c>
-      <c r="F4" s="43">
+      <c r="F4" s="32">
         <v>2.0</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="33">
         <v>-0.2</v>
       </c>
-      <c r="H4" s="45"/>
-      <c r="I4" s="43">
+      <c r="H4" s="35"/>
+      <c r="I4" s="32">
         <v>-50.0</v>
       </c>
-      <c r="J4" s="46"/>
-      <c r="K4" s="47">
+      <c r="J4" s="36"/>
+      <c r="K4" s="37">
         <v>0.0</v>
       </c>
-      <c r="L4" s="48">
+      <c r="L4" s="38">
         <v>2500.0</v>
       </c>
-      <c r="M4" s="49">
+      <c r="M4" s="40">
         <v>-0.022</v>
       </c>
-      <c r="N4" s="49">
+      <c r="N4" s="40">
         <v>111.5</v>
       </c>
-      <c r="O4" s="49">
+      <c r="O4" s="40">
         <v>108.5</v>
       </c>
-      <c r="P4" s="49">
+      <c r="P4" s="40">
         <v>1.0</v>
       </c>
-      <c r="Q4" s="49">
+      <c r="Q4" s="40">
         <v>0.35</v>
       </c>
-      <c r="R4" s="50">
+      <c r="R4" s="41">
         <v>0.55</v>
       </c>
-      <c r="S4" s="51">
+      <c r="S4" s="42">
         <v>2.5</v>
       </c>
-      <c r="T4" s="52">
+      <c r="T4" s="44">
         <f>MAX(MIN($M4*Model!$A$13+$N4,$O4)*$P4,0)</f>
         <v>108.5</v>
       </c>
-      <c r="U4" s="52">
+      <c r="U4" s="44">
         <f>MAX(MIN($M4*Model!$A$14+$N4,$O4)*$P4,0)</f>
         <v>108.5</v>
       </c>
-      <c r="V4" s="52">
+      <c r="V4" s="44">
         <f>MAX(MIN($M4*Model!$A$15+$N4,$O4)*$P4,0)</f>
         <v>107.1</v>
       </c>
-      <c r="W4" s="52">
+      <c r="W4" s="44">
         <f>MAX(MIN($M4*Model!$A$16+$N4,$O4)*$P4,0)</f>
         <v>104.9</v>
       </c>
-      <c r="X4" s="52">
+      <c r="X4" s="44">
         <f>MAX(MIN($M4*Model!$A$17+$N4,$O4)*$P4,0)</f>
         <v>102.7</v>
       </c>
-      <c r="Y4" s="52">
+      <c r="Y4" s="44">
         <f>MAX(MIN($M4*Model!$A$18+$N4,$O4)*$P4,0)</f>
         <v>99.4</v>
       </c>
-      <c r="Z4" s="52">
+      <c r="Z4" s="44">
         <f>MAX(MIN($M4*Model!$A$19+$N4,$O4)*$P4,0)</f>
         <v>95</v>
       </c>
-      <c r="AA4" s="52">
+      <c r="AA4" s="44">
         <f>T4*Model!$B$13+U4*Model!$B$14+V4*Model!$B$15+W4*Model!$B$16+X4*Model!$B$17+Y4*Model!$B$18+Z4*Model!$B$19</f>
         <v>104.755</v>
       </c>
@@ -1865,7 +1695,7 @@
       <c r="AC4" s="53">
         <v>1.1</v>
       </c>
-      <c r="AD4" s="51" t="str">
+      <c r="AD4" s="42" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE4,";",'7.62x54R-ammo'!$AF4,";",'7.62x54R-ammo'!$AG4,";",'7.62x54R-ammo'!$AH4,")")</f>
         <v>stat(bullet_velocity;0.6;1.1;1500;3000)</v>
       </c>
@@ -1885,7 +1715,7 @@
         <f>Model!$B$4+IF(I4="",0,I4)</f>
         <v>2069</v>
       </c>
-      <c r="AJ4" s="52">
+      <c r="AJ4" s="44">
         <f t="shared" si="1"/>
         <v>0.7896666667</v>
       </c>
@@ -1915,88 +1745,88 @@
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="32">
         <v>2.0</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="33">
         <v>0.0</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="32">
         <v>-3.0</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="32">
         <v>-3.0</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="33">
         <v>0.1</v>
       </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="43">
+      <c r="H5" s="35"/>
+      <c r="I5" s="32">
         <v>100.0</v>
       </c>
-      <c r="J5" s="46"/>
-      <c r="K5" s="47">
+      <c r="J5" s="36"/>
+      <c r="K5" s="37">
         <v>0.0</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="38">
         <v>1000.0</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="40">
         <v>-0.026</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="40">
         <v>111.5</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="40">
         <v>112.0</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="40">
         <v>1.0</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="40">
         <v>0.3</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="41">
         <v>0.5</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="42">
         <v>2.5</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="44">
         <f>MAX(MIN($M5*Model!$A$13+$N5,$O5)*$P5,0)</f>
         <v>110.2</v>
       </c>
-      <c r="U5" s="52">
+      <c r="U5" s="44">
         <f>MAX(MIN($M5*Model!$A$14+$N5,$O5)*$P5,0)</f>
         <v>108.9</v>
       </c>
-      <c r="V5" s="52">
+      <c r="V5" s="44">
         <f>MAX(MIN($M5*Model!$A$15+$N5,$O5)*$P5,0)</f>
         <v>106.3</v>
       </c>
-      <c r="W5" s="52">
+      <c r="W5" s="44">
         <f>MAX(MIN($M5*Model!$A$16+$N5,$O5)*$P5,0)</f>
         <v>103.7</v>
       </c>
-      <c r="X5" s="52">
+      <c r="X5" s="44">
         <f>MAX(MIN($M5*Model!$A$17+$N5,$O5)*$P5,0)</f>
         <v>101.1</v>
       </c>
-      <c r="Y5" s="52">
+      <c r="Y5" s="44">
         <f>MAX(MIN($M5*Model!$A$18+$N5,$O5)*$P5,0)</f>
         <v>97.2</v>
       </c>
-      <c r="Z5" s="52">
+      <c r="Z5" s="44">
         <f>MAX(MIN($M5*Model!$A$19+$N5,$O5)*$P5,0)</f>
         <v>92</v>
       </c>
-      <c r="AA5" s="52">
+      <c r="AA5" s="44">
         <f>T5*Model!$B$13+U5*Model!$B$14+V5*Model!$B$15+W5*Model!$B$16+X5*Model!$B$17+Y5*Model!$B$18+Z5*Model!$B$19</f>
         <v>103.895</v>
       </c>
@@ -2006,7 +1836,7 @@
       <c r="AC5" s="53">
         <v>1.5</v>
       </c>
-      <c r="AD5" s="51" t="str">
+      <c r="AD5" s="42" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE5,";",'7.62x54R-ammo'!$AF5,";",'7.62x54R-ammo'!$AG5,";",'7.62x54R-ammo'!$AH5,")")</f>
         <v>stat(bullet_velocity;0.5;1;1500;3000)</v>
       </c>
@@ -2026,7 +1856,7 @@
         <f>Model!$B$4+IF(I5="",0,I5)</f>
         <v>2219</v>
       </c>
-      <c r="AJ5" s="52">
+      <c r="AJ5" s="44">
         <f t="shared" si="1"/>
         <v>0.7396666667</v>
       </c>
@@ -2056,88 +1886,88 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="32">
         <v>0.0</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="33">
         <v>0.0</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="32">
         <v>0.0</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="32">
         <v>0.0</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="33">
         <v>0.0</v>
       </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="43">
+      <c r="H6" s="35"/>
+      <c r="I6" s="32">
         <v>0.0</v>
       </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="47">
+      <c r="J6" s="36"/>
+      <c r="K6" s="37">
         <v>0.0</v>
       </c>
-      <c r="L6" s="48">
+      <c r="L6" s="38">
         <v>0.0</v>
       </c>
-      <c r="M6" s="49">
+      <c r="M6" s="40">
         <v>-0.024</v>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="40">
         <v>112.0</v>
       </c>
-      <c r="O6" s="49">
+      <c r="O6" s="40">
         <v>112.0</v>
       </c>
-      <c r="P6" s="49">
+      <c r="P6" s="40">
         <v>1.0</v>
       </c>
-      <c r="Q6" s="49">
+      <c r="Q6" s="40">
         <v>0.3</v>
       </c>
-      <c r="R6" s="49">
+      <c r="R6" s="40">
         <v>0.5</v>
       </c>
-      <c r="S6" s="51">
+      <c r="S6" s="42">
         <v>2.5</v>
       </c>
-      <c r="T6" s="52">
+      <c r="T6" s="44">
         <f>MAX(MIN($M6*Model!$A$13+$N6,$O6)*$P6,0)</f>
         <v>110.8</v>
       </c>
-      <c r="U6" s="52">
+      <c r="U6" s="44">
         <f>MAX(MIN($M6*Model!$A$14+$N6,$O6)*$P6,0)</f>
         <v>109.6</v>
       </c>
-      <c r="V6" s="52">
+      <c r="V6" s="44">
         <f>MAX(MIN($M6*Model!$A$15+$N6,$O6)*$P6,0)</f>
         <v>107.2</v>
       </c>
-      <c r="W6" s="52">
+      <c r="W6" s="44">
         <f>MAX(MIN($M6*Model!$A$16+$N6,$O6)*$P6,0)</f>
         <v>104.8</v>
       </c>
-      <c r="X6" s="52">
+      <c r="X6" s="44">
         <f>MAX(MIN($M6*Model!$A$17+$N6,$O6)*$P6,0)</f>
         <v>102.4</v>
       </c>
-      <c r="Y6" s="52">
+      <c r="Y6" s="44">
         <f>MAX(MIN($M6*Model!$A$18+$N6,$O6)*$P6,0)</f>
         <v>98.8</v>
       </c>
-      <c r="Z6" s="52">
+      <c r="Z6" s="44">
         <f>MAX(MIN($M6*Model!$A$19+$N6,$O6)*$P6,0)</f>
         <v>94</v>
       </c>
-      <c r="AA6" s="52">
+      <c r="AA6" s="44">
         <f>T6*Model!$B$13+U6*Model!$B$14+V6*Model!$B$15+W6*Model!$B$16+X6*Model!$B$17+Y6*Model!$B$18+Z6*Model!$B$19</f>
         <v>104.98</v>
       </c>
@@ -2147,7 +1977,7 @@
       <c r="AC6" s="53">
         <v>1.0</v>
       </c>
-      <c r="AD6" s="51" t="str">
+      <c r="AD6" s="42" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE6,";",'7.62x54R-ammo'!$AF6,";",'7.62x54R-ammo'!$AG6,";",'7.62x54R-ammo'!$AH6,")")</f>
         <v>stat(bullet_velocity;0.7;1.2;1500;3000)</v>
       </c>
@@ -2167,7 +1997,7 @@
         <f>Model!$B$4+IF(I6="",0,I6)</f>
         <v>2119</v>
       </c>
-      <c r="AJ6" s="52">
+      <c r="AJ6" s="44">
         <f t="shared" si="1"/>
         <v>0.9063333333</v>
       </c>
@@ -2197,88 +2027,88 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="32">
         <v>1.0</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="33">
         <v>0.08</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="32">
         <v>-2.0</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="32">
         <v>-1.0</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="33">
         <v>-0.15</v>
       </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="43">
+      <c r="H7" s="35"/>
+      <c r="I7" s="32">
         <v>-150.0</v>
       </c>
-      <c r="J7" s="46"/>
-      <c r="K7" s="47">
+      <c r="J7" s="36"/>
+      <c r="K7" s="37">
         <v>0.0</v>
       </c>
-      <c r="L7" s="48">
+      <c r="L7" s="38">
         <v>1500.0</v>
       </c>
-      <c r="M7" s="49">
+      <c r="M7" s="40">
         <v>-0.028</v>
       </c>
-      <c r="N7" s="49">
+      <c r="N7" s="40">
         <v>115.5</v>
       </c>
-      <c r="O7" s="49">
+      <c r="O7" s="40">
         <v>115.0</v>
       </c>
-      <c r="P7" s="49">
+      <c r="P7" s="40">
         <v>1.0</v>
       </c>
-      <c r="Q7" s="49">
+      <c r="Q7" s="40">
         <v>0.35</v>
       </c>
-      <c r="R7" s="50">
+      <c r="R7" s="41">
         <v>0.55</v>
       </c>
-      <c r="S7" s="51">
+      <c r="S7" s="42">
         <v>2.5</v>
       </c>
-      <c r="T7" s="52">
+      <c r="T7" s="44">
         <f>MAX(MIN($M7*Model!$A$13+$N7,$O7)*$P7,0)</f>
         <v>114.1</v>
       </c>
-      <c r="U7" s="52">
+      <c r="U7" s="44">
         <f>MAX(MIN($M7*Model!$A$14+$N7,$O7)*$P7,0)</f>
         <v>112.7</v>
       </c>
-      <c r="V7" s="52">
+      <c r="V7" s="44">
         <f>MAX(MIN($M7*Model!$A$15+$N7,$O7)*$P7,0)</f>
         <v>109.9</v>
       </c>
-      <c r="W7" s="52">
+      <c r="W7" s="44">
         <f>MAX(MIN($M7*Model!$A$16+$N7,$O7)*$P7,0)</f>
         <v>107.1</v>
       </c>
-      <c r="X7" s="52">
+      <c r="X7" s="44">
         <f>MAX(MIN($M7*Model!$A$17+$N7,$O7)*$P7,0)</f>
         <v>104.3</v>
       </c>
-      <c r="Y7" s="52">
+      <c r="Y7" s="44">
         <f>MAX(MIN($M7*Model!$A$18+$N7,$O7)*$P7,0)</f>
         <v>100.1</v>
       </c>
-      <c r="Z7" s="52">
+      <c r="Z7" s="44">
         <f>MAX(MIN($M7*Model!$A$19+$N7,$O7)*$P7,0)</f>
         <v>94.5</v>
       </c>
-      <c r="AA7" s="52">
+      <c r="AA7" s="44">
         <f>T7*Model!$B$13+U7*Model!$B$14+V7*Model!$B$15+W7*Model!$B$16+X7*Model!$B$17+Y7*Model!$B$18+Z7*Model!$B$19</f>
         <v>107.31</v>
       </c>
@@ -2288,7 +2118,7 @@
       <c r="AC7" s="53">
         <v>0.9</v>
       </c>
-      <c r="AD7" s="51" t="str">
+      <c r="AD7" s="42" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE7,";",'7.62x54R-ammo'!$AF7,";",'7.62x54R-ammo'!$AG7,";",'7.62x54R-ammo'!$AH7,")")</f>
         <v>stat(bullet_velocity;0.1;0.6;1500;3000)</v>
       </c>
@@ -2308,7 +2138,7 @@
         <f>Model!$B$4+IF(I7="",0,I7)</f>
         <v>1969</v>
       </c>
-      <c r="AJ7" s="52">
+      <c r="AJ7" s="44">
         <f t="shared" si="1"/>
         <v>0.2563333333</v>
       </c>
@@ -2338,88 +2168,88 @@
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="32">
         <v>-1.0</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="33">
         <v>0.01</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="32">
         <v>2.0</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="32">
         <v>2.0</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="33">
         <v>-0.15</v>
       </c>
-      <c r="H8" s="45"/>
-      <c r="I8" s="43">
+      <c r="H8" s="35"/>
+      <c r="I8" s="32">
         <v>-50.0</v>
       </c>
-      <c r="J8" s="46"/>
-      <c r="K8" s="47">
+      <c r="J8" s="36"/>
+      <c r="K8" s="37">
         <v>0.0</v>
       </c>
-      <c r="L8" s="48">
+      <c r="L8" s="38">
         <v>4000.0</v>
       </c>
-      <c r="M8" s="49">
+      <c r="M8" s="40">
         <v>-0.014</v>
       </c>
-      <c r="N8" s="49">
+      <c r="N8" s="40">
         <v>106.0</v>
       </c>
-      <c r="O8" s="49">
+      <c r="O8" s="40">
         <v>105.0</v>
       </c>
-      <c r="P8" s="49">
+      <c r="P8" s="40">
         <v>1.0</v>
       </c>
-      <c r="Q8" s="49">
+      <c r="Q8" s="40">
         <v>0.25</v>
       </c>
-      <c r="R8" s="49">
+      <c r="R8" s="40">
         <v>0.45</v>
       </c>
-      <c r="S8" s="51">
+      <c r="S8" s="42">
         <v>2.5</v>
       </c>
-      <c r="T8" s="52">
+      <c r="T8" s="44">
         <f>MAX(MIN($M8*Model!$A$13+$N8,$O8)*$P8,0)</f>
         <v>105</v>
       </c>
-      <c r="U8" s="52">
+      <c r="U8" s="44">
         <f>MAX(MIN($M8*Model!$A$14+$N8,$O8)*$P8,0)</f>
         <v>104.6</v>
       </c>
-      <c r="V8" s="52">
+      <c r="V8" s="44">
         <f>MAX(MIN($M8*Model!$A$15+$N8,$O8)*$P8,0)</f>
         <v>103.2</v>
       </c>
-      <c r="W8" s="52">
+      <c r="W8" s="44">
         <f>MAX(MIN($M8*Model!$A$16+$N8,$O8)*$P8,0)</f>
         <v>101.8</v>
       </c>
-      <c r="X8" s="52">
+      <c r="X8" s="44">
         <f>MAX(MIN($M8*Model!$A$17+$N8,$O8)*$P8,0)</f>
         <v>100.4</v>
       </c>
-      <c r="Y8" s="52">
+      <c r="Y8" s="44">
         <f>MAX(MIN($M8*Model!$A$18+$N8,$O8)*$P8,0)</f>
         <v>98.3</v>
       </c>
-      <c r="Z8" s="52">
+      <c r="Z8" s="44">
         <f>MAX(MIN($M8*Model!$A$19+$N8,$O8)*$P8,0)</f>
         <v>95.5</v>
       </c>
-      <c r="AA8" s="52">
+      <c r="AA8" s="44">
         <f>T8*Model!$B$13+U8*Model!$B$14+V8*Model!$B$15+W8*Model!$B$16+X8*Model!$B$17+Y8*Model!$B$18+Z8*Model!$B$19</f>
         <v>101.875</v>
       </c>
@@ -2429,7 +2259,7 @@
       <c r="AC8" s="53">
         <v>0.95</v>
       </c>
-      <c r="AD8" s="51" t="str">
+      <c r="AD8" s="42" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE8,";",'7.62x54R-ammo'!$AF8,";",'7.62x54R-ammo'!$AG8,";",'7.62x54R-ammo'!$AH8,")")</f>
         <v>stat(bullet_velocity;1.4;1.9;1500;3000)</v>
       </c>
@@ -2449,7 +2279,7 @@
         <f>Model!$B$4+IF(I8="",0,I8)</f>
         <v>2069</v>
       </c>
-      <c r="AJ8" s="52">
+      <c r="AJ8" s="44">
         <f t="shared" si="1"/>
         <v>1.589666667</v>
       </c>
@@ -2479,88 +2309,88 @@
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="32">
         <v>-2.0</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="33">
         <v>0.08</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="32">
         <v>3.0</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="32">
         <v>7.0</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="33">
         <v>-0.1</v>
       </c>
-      <c r="H9" s="60"/>
-      <c r="I9" s="43">
+      <c r="H9" s="59"/>
+      <c r="I9" s="32">
         <v>200.0</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="47">
+      <c r="J9" s="60"/>
+      <c r="K9" s="37">
         <v>0.0</v>
       </c>
-      <c r="L9" s="48">
+      <c r="L9" s="38">
         <v>5000.0</v>
       </c>
-      <c r="M9" s="49">
+      <c r="M9" s="40">
         <v>-0.012</v>
       </c>
-      <c r="N9" s="49">
+      <c r="N9" s="40">
         <v>104.5</v>
       </c>
-      <c r="O9" s="49">
+      <c r="O9" s="40">
         <v>102.5</v>
       </c>
-      <c r="P9" s="49">
+      <c r="P9" s="40">
         <v>1.0</v>
       </c>
-      <c r="Q9" s="49">
+      <c r="Q9" s="40">
         <v>0.2</v>
       </c>
-      <c r="R9" s="49">
+      <c r="R9" s="40">
         <v>0.4</v>
       </c>
-      <c r="S9" s="62">
+      <c r="S9" s="61">
         <v>2.5</v>
       </c>
-      <c r="T9" s="63">
+      <c r="T9" s="62">
         <f>MAX(MIN($M9*Model!$A$13+$N9,$O9)*$P9,0)</f>
         <v>102.5</v>
       </c>
-      <c r="U9" s="63">
+      <c r="U9" s="62">
         <f>MAX(MIN($M9*Model!$A$14+$N9,$O9)*$P9,0)</f>
         <v>102.5</v>
       </c>
-      <c r="V9" s="63">
+      <c r="V9" s="62">
         <f>MAX(MIN($M9*Model!$A$15+$N9,$O9)*$P9,0)</f>
         <v>102.1</v>
       </c>
-      <c r="W9" s="63">
+      <c r="W9" s="62">
         <f>MAX(MIN($M9*Model!$A$16+$N9,$O9)*$P9,0)</f>
         <v>100.9</v>
       </c>
-      <c r="X9" s="63">
+      <c r="X9" s="62">
         <f>MAX(MIN($M9*Model!$A$17+$N9,$O9)*$P9,0)</f>
         <v>99.7</v>
       </c>
-      <c r="Y9" s="63">
+      <c r="Y9" s="62">
         <f>MAX(MIN($M9*Model!$A$18+$N9,$O9)*$P9,0)</f>
         <v>97.9</v>
       </c>
-      <c r="Z9" s="63">
+      <c r="Z9" s="62">
         <f>MAX(MIN($M9*Model!$A$19+$N9,$O9)*$P9,0)</f>
         <v>95.5</v>
       </c>
-      <c r="AA9" s="63">
+      <c r="AA9" s="62">
         <f>T9*Model!$B$13+U9*Model!$B$14+V9*Model!$B$15+W9*Model!$B$16+X9*Model!$B$17+Y9*Model!$B$18+Z9*Model!$B$19</f>
         <v>100.73</v>
       </c>
@@ -2570,7 +2400,7 @@
       <c r="AC9" s="53">
         <v>1.2</v>
       </c>
-      <c r="AD9" s="62" t="str">
+      <c r="AD9" s="61" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE9,";",'7.62x54R-ammo'!$AF9,";",'7.62x54R-ammo'!$AG9,";",'7.62x54R-ammo'!$AH9,")")</f>
         <v>stat(bullet_velocity;1.9;2.4;1500;3000)</v>
       </c>
@@ -2580,17 +2410,17 @@
       <c r="AF9" s="54">
         <v>2.4</v>
       </c>
-      <c r="AG9" s="64">
+      <c r="AG9" s="63">
         <v>1500.0</v>
       </c>
-      <c r="AH9" s="64">
+      <c r="AH9" s="63">
         <v>3000.0</v>
       </c>
-      <c r="AI9" s="65">
+      <c r="AI9" s="64">
         <f>Model!$B$4+IF(I9="",0,I9)</f>
         <v>2319</v>
       </c>
-      <c r="AJ9" s="63">
+      <c r="AJ9" s="62">
         <f t="shared" si="1"/>
         <v>2.173</v>
       </c>
@@ -2598,110 +2428,110 @@
         <f>C9*Model!$B$24+D9*Model!$B$25+E9*Model!$B$26+F9*Model!$B$27+G9*Model!$B$28+H9*Model!$B$29+I9*Model!$B$30+J9*Model!$B$31+L9*Model!$B$32+K9*Model!$B$33</f>
         <v>-2.9</v>
       </c>
-      <c r="AL9" s="66">
+      <c r="AL9" s="65">
         <f>(AA9-Model!$B$5)*Model!$B$35</f>
         <v>0.365</v>
       </c>
-      <c r="AM9" s="66">
+      <c r="AM9" s="65">
         <f>(Model!$B$6-AB9)*Model!$B$36</f>
         <v>0.1</v>
       </c>
-      <c r="AN9" s="66">
+      <c r="AN9" s="65">
         <f>(AC9-Model!$B$7)*Model!$B$37</f>
         <v>1.05</v>
       </c>
-      <c r="AO9" s="66">
+      <c r="AO9" s="65">
         <f>(AJ9-Model!$B$8)*Model!$B$38</f>
         <v>7.038</v>
       </c>
-      <c r="AP9" s="66">
+      <c r="AP9" s="65">
         <f t="shared" si="2"/>
         <v>5.653</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="32">
         <v>-2.0</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="33">
         <v>0.02</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="32">
         <v>2.0</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="32">
         <v>3.0</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="33">
         <v>0.05</v>
       </c>
-      <c r="H10" s="45"/>
-      <c r="I10" s="43">
+      <c r="H10" s="35"/>
+      <c r="I10" s="32">
         <v>0.0</v>
       </c>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47">
+      <c r="J10" s="37"/>
+      <c r="K10" s="37">
         <v>0.0</v>
       </c>
-      <c r="L10" s="48">
+      <c r="L10" s="38">
         <v>3000.0</v>
       </c>
-      <c r="M10" s="49">
+      <c r="M10" s="40">
         <v>-0.018</v>
       </c>
-      <c r="N10" s="49">
+      <c r="N10" s="40">
         <v>105.5</v>
       </c>
-      <c r="O10" s="49">
+      <c r="O10" s="40">
         <v>104.0</v>
       </c>
-      <c r="P10" s="49">
+      <c r="P10" s="40">
         <v>1.0</v>
       </c>
-      <c r="Q10" s="49">
+      <c r="Q10" s="40">
         <v>0.25</v>
       </c>
-      <c r="R10" s="49">
+      <c r="R10" s="40">
         <v>0.45</v>
       </c>
-      <c r="S10" s="51">
+      <c r="S10" s="42">
         <v>2.5</v>
       </c>
-      <c r="T10" s="52">
+      <c r="T10" s="44">
         <f>MAX(MIN($M10*Model!$A$13+$N10,$O10)*$P10,0)</f>
         <v>104</v>
       </c>
-      <c r="U10" s="52">
+      <c r="U10" s="44">
         <f>MAX(MIN($M10*Model!$A$14+$N10,$O10)*$P10,0)</f>
         <v>103.7</v>
       </c>
-      <c r="V10" s="52">
+      <c r="V10" s="44">
         <f>MAX(MIN($M10*Model!$A$15+$N10,$O10)*$P10,0)</f>
         <v>101.9</v>
       </c>
-      <c r="W10" s="52">
+      <c r="W10" s="44">
         <f>MAX(MIN($M10*Model!$A$16+$N10,$O10)*$P10,0)</f>
         <v>100.1</v>
       </c>
-      <c r="X10" s="52">
+      <c r="X10" s="44">
         <f>MAX(MIN($M10*Model!$A$17+$N10,$O10)*$P10,0)</f>
         <v>98.3</v>
       </c>
-      <c r="Y10" s="52">
+      <c r="Y10" s="44">
         <f>MAX(MIN($M10*Model!$A$18+$N10,$O10)*$P10,0)</f>
         <v>95.6</v>
       </c>
-      <c r="Z10" s="52">
+      <c r="Z10" s="44">
         <f>MAX(MIN($M10*Model!$A$19+$N10,$O10)*$P10,0)</f>
         <v>92</v>
       </c>
-      <c r="AA10" s="52">
+      <c r="AA10" s="44">
         <f>T10*Model!$B$13+U10*Model!$B$14+V10*Model!$B$15+W10*Model!$B$16+X10*Model!$B$17+Y10*Model!$B$18+Z10*Model!$B$19</f>
         <v>100.175</v>
       </c>
@@ -2711,7 +2541,7 @@
       <c r="AC10" s="53">
         <v>1.0</v>
       </c>
-      <c r="AD10" s="51" t="str">
+      <c r="AD10" s="42" t="str">
         <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE10,";",'7.62x54R-ammo'!$AF10,";",'7.62x54R-ammo'!$AG10,";",'7.62x54R-ammo'!$AH10,")")</f>
         <v>stat(bullet_velocity;1.1;1.6;1500;3000)</v>
       </c>
@@ -2731,7 +2561,7 @@
         <f>Model!$B$4+IF(I10="",0,I10)</f>
         <v>2119</v>
       </c>
-      <c r="AJ10" s="52">
+      <c r="AJ10" s="44">
         <f t="shared" si="1"/>
         <v>1.306333333</v>
       </c>
@@ -2761,130 +2591,189 @@
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="67"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="69" t="s">
+      <c r="A11" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="70"/>
-      <c r="I11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="J11" s="71"/>
-      <c r="K11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="L11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="M11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="N11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="O11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="P11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="R11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="S11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="T11" s="71"/>
-      <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
-      <c r="W11" s="71"/>
-      <c r="X11" s="71"/>
-      <c r="Y11" s="71"/>
-      <c r="Z11" s="71"/>
-      <c r="AA11" s="71"/>
-      <c r="AB11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD11" s="72"/>
-      <c r="AE11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF11" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG11" s="73"/>
-      <c r="AH11" s="73"/>
-      <c r="AI11" s="73"/>
-      <c r="AJ11" s="71"/>
-      <c r="AK11" s="71"/>
-      <c r="AL11" s="71"/>
-      <c r="AM11" s="71"/>
-      <c r="AN11" s="71"/>
-      <c r="AO11" s="71"/>
-      <c r="AP11" s="71"/>
+      <c r="B11" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="32">
+        <v>3.0</v>
+      </c>
+      <c r="D11" s="33">
+        <v>0.14</v>
+      </c>
+      <c r="E11" s="32">
+        <v>-3.0</v>
+      </c>
+      <c r="F11" s="32">
+        <v>-3.0</v>
+      </c>
+      <c r="G11" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="32">
+        <v>-950.0</v>
+      </c>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37">
+        <v>-0.6</v>
+      </c>
+      <c r="L11" s="38">
+        <v>2500.0</v>
+      </c>
+      <c r="M11" s="40">
+        <v>-0.028</v>
+      </c>
+      <c r="N11" s="66">
+        <v>111.0</v>
+      </c>
+      <c r="O11" s="66">
+        <v>111.0</v>
+      </c>
+      <c r="P11" s="40">
+        <v>1.0</v>
+      </c>
+      <c r="Q11" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="R11" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="S11" s="42">
+        <v>2.5</v>
+      </c>
+      <c r="T11" s="44">
+        <f>MAX(MIN($M11*Model!$A$13+$N11,$O11)*$P11,0)</f>
+        <v>109.6</v>
+      </c>
+      <c r="U11" s="44">
+        <f>MAX(MIN($M11*Model!$A$14+$N11,$O11)*$P11,0)</f>
+        <v>108.2</v>
+      </c>
+      <c r="V11" s="44">
+        <f>MAX(MIN($M11*Model!$A$15+$N11,$O11)*$P11,0)</f>
+        <v>105.4</v>
+      </c>
+      <c r="W11" s="44">
+        <f>MAX(MIN($M11*Model!$A$16+$N11,$O11)*$P11,0)</f>
+        <v>102.6</v>
+      </c>
+      <c r="X11" s="44">
+        <f>MAX(MIN($M11*Model!$A$17+$N11,$O11)*$P11,0)</f>
+        <v>99.8</v>
+      </c>
+      <c r="Y11" s="44">
+        <f>MAX(MIN($M11*Model!$A$18+$N11,$O11)*$P11,0)</f>
+        <v>95.6</v>
+      </c>
+      <c r="Z11" s="44">
+        <f>MAX(MIN($M11*Model!$A$19+$N11,$O11)*$P11,0)</f>
+        <v>90</v>
+      </c>
+      <c r="AA11" s="44">
+        <f>T11*Model!$B$13+U11*Model!$B$14+V11*Model!$B$15+W11*Model!$B$16+X11*Model!$B$17+Y11*Model!$B$18+Z11*Model!$B$19</f>
+        <v>102.81</v>
+      </c>
+      <c r="AB11" s="53">
+        <v>0.7</v>
+      </c>
+      <c r="AC11" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="AD11" s="42" t="str">
+        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE11,";",'7.62x54R-ammo'!$AF11,";",'7.62x54R-ammo'!$AG11,";",'7.62x54R-ammo'!$AH11,")")</f>
+        <v>stat(bullet_velocity;0.3;0.7;1500;3000)</v>
+      </c>
+      <c r="AE11" s="54">
+        <v>0.3</v>
+      </c>
+      <c r="AF11" s="54">
+        <v>0.7</v>
+      </c>
+      <c r="AG11" s="55">
+        <v>1500.0</v>
+      </c>
+      <c r="AH11" s="55">
+        <v>3000.0</v>
+      </c>
+      <c r="AI11" s="56">
+        <f>Model!$B$4+IF(I11="",0,I11)</f>
+        <v>1169</v>
+      </c>
+      <c r="AJ11" s="44">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="AK11" s="57">
+        <f>C11*Model!$B$24+D11*Model!$B$25+E11*Model!$B$26+F11*Model!$B$27+G11*Model!$B$28+H11*Model!$B$29+I11*Model!$B$30+J11*Model!$B$31+L11*Model!$B$32+K11*Model!$B$33</f>
+        <v>2.05</v>
+      </c>
+      <c r="AL11" s="57">
+        <f>(AA11-Model!$B$5)*Model!$B$35</f>
+        <v>1.405</v>
+      </c>
+      <c r="AM11" s="57">
+        <f>(Model!$B$6-AB11)*Model!$B$36</f>
+        <v>-0.7</v>
+      </c>
+      <c r="AN11" s="57">
+        <f>(AC11-Model!$B$7)*Model!$B$37</f>
+        <v>-1.8</v>
+      </c>
+      <c r="AO11" s="57">
+        <f>(AJ11-Model!$B$8)*Model!$B$38</f>
+        <v>-4.2</v>
+      </c>
+      <c r="AP11" s="57">
+        <f t="shared" si="2"/>
+        <v>-3.245</v>
+      </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="67"/>
       <c r="B12" s="68"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="75"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="76"/>
-      <c r="O12" s="76"/>
-      <c r="P12" s="76"/>
-      <c r="Q12" s="76"/>
-      <c r="R12" s="76"/>
-      <c r="S12" s="76"/>
-      <c r="T12" s="71"/>
-      <c r="U12" s="71"/>
-      <c r="V12" s="71"/>
-      <c r="W12" s="71"/>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="71"/>
-      <c r="AA12" s="71"/>
-      <c r="AB12" s="77"/>
-      <c r="AC12" s="77"/>
-      <c r="AD12" s="72"/>
-      <c r="AE12" s="69"/>
-      <c r="AF12" s="69"/>
-      <c r="AG12" s="73"/>
-      <c r="AH12" s="73"/>
-      <c r="AI12" s="73"/>
-      <c r="AJ12" s="71"/>
-      <c r="AK12" s="71"/>
-      <c r="AL12" s="71"/>
-      <c r="AM12" s="71"/>
-      <c r="AN12" s="71"/>
-      <c r="AO12" s="71"/>
-      <c r="AP12" s="71"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="74"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="74"/>
+      <c r="P12" s="74"/>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="74"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="72"/>
+      <c r="V12" s="72"/>
+      <c r="W12" s="72"/>
+      <c r="X12" s="72"/>
+      <c r="Y12" s="72"/>
+      <c r="Z12" s="72"/>
+      <c r="AA12" s="72"/>
+      <c r="AB12" s="75"/>
+      <c r="AC12" s="75"/>
+      <c r="AD12" s="76"/>
+      <c r="AE12" s="70"/>
+      <c r="AF12" s="70"/>
+      <c r="AG12" s="77"/>
+      <c r="AH12" s="77"/>
+      <c r="AI12" s="77"/>
+      <c r="AJ12" s="72"/>
+      <c r="AK12" s="72"/>
+      <c r="AL12" s="72"/>
+      <c r="AM12" s="72"/>
+      <c r="AN12" s="72"/>
+      <c r="AO12" s="72"/>
+      <c r="AP12" s="72"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="78"/>
@@ -2893,12 +2782,12 @@
       <c r="D13" s="80"/>
       <c r="E13" s="80"/>
       <c r="F13" s="80"/>
-      <c r="G13" s="75"/>
+      <c r="G13" s="73"/>
       <c r="H13" s="81"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="75"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="73"/>
       <c r="M13" s="82"/>
       <c r="N13" s="82"/>
       <c r="O13" s="82"/>
@@ -2936,15 +2825,15 @@
       <c r="C14" s="80"/>
       <c r="D14" s="80"/>
       <c r="E14" s="80"/>
-      <c r="F14" s="75"/>
+      <c r="F14" s="73"/>
       <c r="G14" s="80"/>
       <c r="H14" s="81"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="75"/>
-      <c r="K14" s="75"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
       <c r="L14" s="80"/>
       <c r="M14" s="82"/>
-      <c r="N14" s="76"/>
+      <c r="N14" s="74"/>
       <c r="O14" s="82"/>
       <c r="P14" s="82"/>
       <c r="Q14" s="82"/>
@@ -2980,15 +2869,15 @@
       <c r="C15" s="80"/>
       <c r="D15" s="80"/>
       <c r="E15" s="80"/>
-      <c r="F15" s="75"/>
+      <c r="F15" s="73"/>
       <c r="G15" s="80"/>
       <c r="H15" s="81"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
       <c r="L15" s="80"/>
       <c r="M15" s="82"/>
-      <c r="N15" s="76"/>
+      <c r="N15" s="74"/>
       <c r="O15" s="82"/>
       <c r="P15" s="82"/>
       <c r="Q15" s="82"/>
@@ -3024,15 +2913,15 @@
       <c r="C16" s="80"/>
       <c r="D16" s="80"/>
       <c r="E16" s="80"/>
-      <c r="F16" s="75"/>
+      <c r="F16" s="73"/>
       <c r="G16" s="80"/>
       <c r="H16" s="81"/>
       <c r="I16" s="80"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="75"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
       <c r="L16" s="80"/>
       <c r="M16" s="82"/>
-      <c r="N16" s="76"/>
+      <c r="N16" s="74"/>
       <c r="O16" s="82"/>
       <c r="P16" s="82"/>
       <c r="Q16" s="82"/>
@@ -3068,7 +2957,7 @@
       <c r="C17" s="80"/>
       <c r="D17" s="80"/>
       <c r="E17" s="80"/>
-      <c r="F17" s="75"/>
+      <c r="F17" s="73"/>
       <c r="G17" s="80"/>
       <c r="H17" s="81"/>
       <c r="I17" s="80"/>
@@ -3112,7 +3001,7 @@
       <c r="C18" s="80"/>
       <c r="D18" s="85"/>
       <c r="E18" s="80"/>
-      <c r="F18" s="75"/>
+      <c r="F18" s="73"/>
       <c r="G18" s="80"/>
       <c r="H18" s="81"/>
       <c r="I18" s="80"/>
@@ -3158,7 +3047,7 @@
       <c r="E19" s="80"/>
       <c r="F19" s="80"/>
       <c r="G19" s="80"/>
-      <c r="H19" s="75"/>
+      <c r="H19" s="73"/>
       <c r="I19" s="80"/>
       <c r="J19" s="80"/>
       <c r="K19" s="80"/>
@@ -3212,1278 +3101,403 @@
     <row r="35" ht="14.25" customHeight="1"/>
     <row r="36" ht="14.25" customHeight="1"/>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="87" t="s">
-        <v>101</v>
-      </c>
+      <c r="A37" s="87"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="88" t="s">
-        <v>102</v>
-      </c>
-      <c r="B38" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="D38" s="44">
-        <v>0.0</v>
-      </c>
-      <c r="E38" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="F38" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="G38" s="44">
-        <v>0.0</v>
-      </c>
-      <c r="H38" s="45"/>
-      <c r="I38" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="J38" s="46"/>
-      <c r="K38" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="L38" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="M38" s="89">
-        <v>-0.026</v>
-      </c>
-      <c r="N38" s="49">
-        <v>104.5</v>
-      </c>
-      <c r="O38" s="49">
-        <v>104.0</v>
-      </c>
-      <c r="P38" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="Q38" s="49">
-        <v>0.3</v>
-      </c>
-      <c r="R38" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="S38" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="T38" s="52">
-        <f>MAX(MIN($M38*Model!$A$13+$N38,$O38)*$P38,0)</f>
-        <v>103.2</v>
-      </c>
-      <c r="U38" s="52">
-        <f>MAX(MIN($M38*Model!$A$14+$N38,$O38)*$P38,0)</f>
-        <v>101.9</v>
-      </c>
-      <c r="V38" s="52">
-        <f>MAX(MIN($M38*Model!$A$15+$N38,$O38)*$P38,0)</f>
-        <v>99.3</v>
-      </c>
-      <c r="W38" s="52">
-        <f>MAX(MIN($M38*Model!$A$16+$N38,$O38)*$P38,0)</f>
-        <v>96.7</v>
-      </c>
-      <c r="X38" s="52">
-        <f>MAX(MIN($M38*Model!$A$17+$N38,$O38)*$P38,0)</f>
-        <v>94.1</v>
-      </c>
-      <c r="Y38" s="52">
-        <f>MAX(MIN($M38*Model!$A$18+$N38,$O38)*$P38,0)</f>
-        <v>90.2</v>
-      </c>
-      <c r="Z38" s="52">
-        <f>MAX(MIN($M38*Model!$A$19+$N38,$O38)*$P38,0)</f>
-        <v>85</v>
-      </c>
-      <c r="AA38" s="52">
-        <f>T38*Model!$B$13+U38*Model!$B$14+V38*Model!$B$15+W38*Model!$B$16+X38*Model!$B$17+Y38*Model!$B$18+Z38*Model!$B$19</f>
-        <v>96.895</v>
-      </c>
-      <c r="AB38" s="53">
-        <v>0.3</v>
-      </c>
-      <c r="AC38" s="53">
-        <v>1.2</v>
-      </c>
-      <c r="AD38" s="51" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE38,";",'7.62x54R-ammo'!$AF38,";",'7.62x54R-ammo'!$AG38,";",'7.62x54R-ammo'!$AH38,")")</f>
-        <v>stat(bullet_velocity;0.6;1.1;1500;3000)</v>
-      </c>
-      <c r="AE38" s="54">
-        <v>0.6</v>
-      </c>
-      <c r="AF38" s="54">
-        <v>1.1</v>
-      </c>
-      <c r="AG38" s="55">
-        <v>1500.0</v>
-      </c>
-      <c r="AH38" s="55">
-        <v>3000.0</v>
-      </c>
-      <c r="AI38" s="56">
-        <f>Model!$B$4+IF(I38="",0,I38)</f>
-        <v>2119</v>
-      </c>
-      <c r="AJ38" s="52">
-        <f t="shared" ref="AJ38:AJ46" si="3">MAX(AE38,MIN(AF38,AE38+(AI38-AG38)*(AF38-AE38)/(AH38-AG38)))</f>
-        <v>0.8063333333</v>
-      </c>
-      <c r="AK38" s="57">
-        <f>C38*Model!$B$24+D38*Model!$B$25+E38*Model!$B$26+F38*Model!$B$27+G38*Model!$B$28+H38*Model!$B$29+I38*Model!$B$30+J38*Model!$B$31+L38*Model!$B$32+K38*Model!$B$33</f>
-        <v>0</v>
-      </c>
-      <c r="AL38" s="57">
-        <f>(AA38-Model!$B$5)*Model!$B$35</f>
-        <v>-1.5525</v>
-      </c>
-      <c r="AM38" s="57">
-        <f>(Model!$B$6-AB38)*Model!$B$36</f>
-        <v>0.1</v>
-      </c>
-      <c r="AN38" s="57">
-        <f>(AC38-Model!$B$7)*Model!$B$37</f>
-        <v>1.05</v>
-      </c>
-      <c r="AO38" s="57">
-        <f>(AJ38-Model!$B$8)*Model!$B$38</f>
-        <v>-1.162</v>
-      </c>
-      <c r="AP38" s="57">
-        <f t="shared" ref="AP38:AP46" si="4">SUM(AK38:AO38)</f>
-        <v>-1.5645</v>
-      </c>
+      <c r="A38" s="30"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="66"/>
+      <c r="N38" s="40"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="40"/>
+      <c r="Q38" s="40"/>
+      <c r="R38" s="41"/>
+      <c r="S38" s="42"/>
+      <c r="T38" s="44"/>
+      <c r="U38" s="44"/>
+      <c r="V38" s="44"/>
+      <c r="W38" s="44"/>
+      <c r="X38" s="44"/>
+      <c r="Y38" s="44"/>
+      <c r="Z38" s="44"/>
+      <c r="AA38" s="44"/>
+      <c r="AB38" s="53"/>
+      <c r="AC38" s="53"/>
+      <c r="AD38" s="42"/>
+      <c r="AE38" s="54"/>
+      <c r="AF38" s="54"/>
+      <c r="AG38" s="55"/>
+      <c r="AH38" s="55"/>
+      <c r="AI38" s="56"/>
+      <c r="AJ38" s="44"/>
+      <c r="AK38" s="57"/>
+      <c r="AL38" s="57"/>
+      <c r="AM38" s="57"/>
+      <c r="AN38" s="57"/>
+      <c r="AO38" s="57"/>
+      <c r="AP38" s="57"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="88" t="s">
-        <v>104</v>
-      </c>
-      <c r="B39" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="43">
-        <v>2.0</v>
-      </c>
-      <c r="D39" s="44">
-        <v>-0.01</v>
-      </c>
-      <c r="E39" s="43">
-        <v>-2.0</v>
-      </c>
-      <c r="F39" s="43">
-        <v>-1.0</v>
-      </c>
-      <c r="G39" s="44">
-        <v>0.1</v>
-      </c>
-      <c r="H39" s="45"/>
-      <c r="I39" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="J39" s="46"/>
-      <c r="K39" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="L39" s="48">
-        <v>500.0</v>
-      </c>
-      <c r="M39" s="49">
-        <v>-0.028</v>
-      </c>
-      <c r="N39" s="49">
-        <v>104.5</v>
-      </c>
-      <c r="O39" s="89">
-        <v>104.0</v>
-      </c>
-      <c r="P39" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="Q39" s="49">
-        <v>0.3</v>
-      </c>
-      <c r="R39" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="S39" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="T39" s="52">
-        <f>MAX(MIN($M39*Model!$A$13+$N39,$O39)*$P39,0)</f>
-        <v>103.1</v>
-      </c>
-      <c r="U39" s="52">
-        <f>MAX(MIN($M39*Model!$A$14+$N39,$O39)*$P39,0)</f>
-        <v>101.7</v>
-      </c>
-      <c r="V39" s="52">
-        <f>MAX(MIN($M39*Model!$A$15+$N39,$O39)*$P39,0)</f>
-        <v>98.9</v>
-      </c>
-      <c r="W39" s="52">
-        <f>MAX(MIN($M39*Model!$A$16+$N39,$O39)*$P39,0)</f>
-        <v>96.1</v>
-      </c>
-      <c r="X39" s="52">
-        <f>MAX(MIN($M39*Model!$A$17+$N39,$O39)*$P39,0)</f>
-        <v>93.3</v>
-      </c>
-      <c r="Y39" s="52">
-        <f>MAX(MIN($M39*Model!$A$18+$N39,$O39)*$P39,0)</f>
-        <v>89.1</v>
-      </c>
-      <c r="Z39" s="52">
-        <f>MAX(MIN($M39*Model!$A$19+$N39,$O39)*$P39,0)</f>
-        <v>83.5</v>
-      </c>
-      <c r="AA39" s="52">
-        <f>T39*Model!$B$13+U39*Model!$B$14+V39*Model!$B$15+W39*Model!$B$16+X39*Model!$B$17+Y39*Model!$B$18+Z39*Model!$B$19</f>
-        <v>96.31</v>
-      </c>
-      <c r="AB39" s="53">
-        <v>0.35</v>
-      </c>
-      <c r="AC39" s="53">
-        <v>1.35</v>
-      </c>
-      <c r="AD39" s="51" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE39,";",'7.62x54R-ammo'!$AF39,";",'7.62x54R-ammo'!$AG39,";",'7.62x54R-ammo'!$AH39,")")</f>
-        <v>stat(bullet_velocity;0.55;1.05;1500;3000)</v>
-      </c>
-      <c r="AE39" s="54">
-        <v>0.55</v>
-      </c>
-      <c r="AF39" s="54">
-        <v>1.05</v>
-      </c>
-      <c r="AG39" s="55">
-        <v>1500.0</v>
-      </c>
-      <c r="AH39" s="55">
-        <v>3000.0</v>
-      </c>
-      <c r="AI39" s="56">
-        <f>Model!$B$4+IF(I39="",0,I39)</f>
-        <v>2119</v>
-      </c>
-      <c r="AJ39" s="52">
-        <f t="shared" si="3"/>
-        <v>0.7563333333</v>
-      </c>
-      <c r="AK39" s="57">
-        <f>C39*Model!$B$24+D39*Model!$B$25+E39*Model!$B$26+F39*Model!$B$27+G39*Model!$B$28+H39*Model!$B$29+I39*Model!$B$30+J39*Model!$B$31+L39*Model!$B$32+K39*Model!$B$33</f>
-        <v>0.3</v>
-      </c>
-      <c r="AL39" s="57">
-        <f>(AA39-Model!$B$5)*Model!$B$35</f>
-        <v>-1.845</v>
-      </c>
-      <c r="AM39" s="57">
-        <f>(Model!$B$6-AB39)*Model!$B$36</f>
-        <v>0</v>
-      </c>
-      <c r="AN39" s="57">
-        <f>(AC39-Model!$B$7)*Model!$B$37</f>
-        <v>1.5</v>
-      </c>
-      <c r="AO39" s="57">
-        <f>(AJ39-Model!$B$8)*Model!$B$38</f>
-        <v>-1.462</v>
-      </c>
-      <c r="AP39" s="57">
-        <f t="shared" si="4"/>
-        <v>-1.507</v>
-      </c>
+      <c r="A39" s="30"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="37"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="40"/>
+      <c r="O39" s="66"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
+      <c r="R39" s="41"/>
+      <c r="S39" s="42"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="44"/>
+      <c r="V39" s="44"/>
+      <c r="W39" s="44"/>
+      <c r="X39" s="44"/>
+      <c r="Y39" s="44"/>
+      <c r="Z39" s="44"/>
+      <c r="AA39" s="44"/>
+      <c r="AB39" s="53"/>
+      <c r="AC39" s="53"/>
+      <c r="AD39" s="42"/>
+      <c r="AE39" s="54"/>
+      <c r="AF39" s="54"/>
+      <c r="AG39" s="55"/>
+      <c r="AH39" s="55"/>
+      <c r="AI39" s="56"/>
+      <c r="AJ39" s="44"/>
+      <c r="AK39" s="57"/>
+      <c r="AL39" s="57"/>
+      <c r="AM39" s="57"/>
+      <c r="AN39" s="57"/>
+      <c r="AO39" s="57"/>
+      <c r="AP39" s="57"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="B40" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="D40" s="44">
-        <v>0.05</v>
-      </c>
-      <c r="E40" s="43">
-        <v>2.0</v>
-      </c>
-      <c r="F40" s="43">
-        <v>2.0</v>
-      </c>
-      <c r="G40" s="44">
-        <v>-0.15</v>
-      </c>
-      <c r="H40" s="45"/>
-      <c r="I40" s="43">
-        <v>-50.0</v>
-      </c>
-      <c r="J40" s="46"/>
-      <c r="K40" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="L40" s="48">
-        <v>1000.0</v>
-      </c>
-      <c r="M40" s="89">
-        <v>-0.026</v>
-      </c>
-      <c r="N40" s="89">
-        <v>105.5</v>
-      </c>
-      <c r="O40" s="89">
-        <v>105.5</v>
-      </c>
-      <c r="P40" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="Q40" s="49">
-        <v>0.3</v>
-      </c>
-      <c r="R40" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="S40" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="T40" s="52">
-        <f>MAX(MIN($M40*Model!$A$13+$N40,$O40)*$P40,0)</f>
-        <v>104.2</v>
-      </c>
-      <c r="U40" s="52">
-        <f>MAX(MIN($M40*Model!$A$14+$N40,$O40)*$P40,0)</f>
-        <v>102.9</v>
-      </c>
-      <c r="V40" s="52">
-        <f>MAX(MIN($M40*Model!$A$15+$N40,$O40)*$P40,0)</f>
-        <v>100.3</v>
-      </c>
-      <c r="W40" s="52">
-        <f>MAX(MIN($M40*Model!$A$16+$N40,$O40)*$P40,0)</f>
-        <v>97.7</v>
-      </c>
-      <c r="X40" s="52">
-        <f>MAX(MIN($M40*Model!$A$17+$N40,$O40)*$P40,0)</f>
-        <v>95.1</v>
-      </c>
-      <c r="Y40" s="52">
-        <f>MAX(MIN($M40*Model!$A$18+$N40,$O40)*$P40,0)</f>
-        <v>91.2</v>
-      </c>
-      <c r="Z40" s="52">
-        <f>MAX(MIN($M40*Model!$A$19+$N40,$O40)*$P40,0)</f>
-        <v>86</v>
-      </c>
-      <c r="AA40" s="52">
-        <f>T40*Model!$B$13+U40*Model!$B$14+V40*Model!$B$15+W40*Model!$B$16+X40*Model!$B$17+Y40*Model!$B$18+Z40*Model!$B$19</f>
-        <v>97.895</v>
-      </c>
-      <c r="AB40" s="53">
-        <v>0.45</v>
-      </c>
-      <c r="AC40" s="53">
-        <v>1.1</v>
-      </c>
-      <c r="AD40" s="51" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE40,";",'7.62x54R-ammo'!$AF40,";",'7.62x54R-ammo'!$AG40,";",'7.62x54R-ammo'!$AH40,")")</f>
-        <v>stat(bullet_velocity;0.2;0.7;1500;3000)</v>
-      </c>
-      <c r="AE40" s="54">
-        <v>0.2</v>
-      </c>
-      <c r="AF40" s="54">
-        <v>0.7</v>
-      </c>
-      <c r="AG40" s="55">
-        <v>1500.0</v>
-      </c>
-      <c r="AH40" s="55">
-        <v>3000.0</v>
-      </c>
-      <c r="AI40" s="56">
-        <f>Model!$B$4+IF(I40="",0,I40)</f>
-        <v>2069</v>
-      </c>
-      <c r="AJ40" s="52">
-        <f t="shared" si="3"/>
-        <v>0.3896666667</v>
-      </c>
-      <c r="AK40" s="57">
-        <f>C40*Model!$B$24+D40*Model!$B$25+E40*Model!$B$26+F40*Model!$B$27+G40*Model!$B$28+H40*Model!$B$29+I40*Model!$B$30+J40*Model!$B$31+L40*Model!$B$32+K40*Model!$B$33</f>
-        <v>1.85</v>
-      </c>
-      <c r="AL40" s="57">
-        <f>(AA40-Model!$B$5)*Model!$B$35</f>
-        <v>-1.0525</v>
-      </c>
-      <c r="AM40" s="57">
-        <f>(Model!$B$6-AB40)*Model!$B$36</f>
-        <v>-0.2</v>
-      </c>
-      <c r="AN40" s="57">
-        <f>(AC40-Model!$B$7)*Model!$B$37</f>
-        <v>0.75</v>
-      </c>
-      <c r="AO40" s="57">
-        <f>(AJ40-Model!$B$8)*Model!$B$38</f>
-        <v>-3.662</v>
-      </c>
-      <c r="AP40" s="57">
-        <f t="shared" si="4"/>
-        <v>-2.3145</v>
-      </c>
+      <c r="A40" s="88"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="66"/>
+      <c r="N40" s="66"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="40"/>
+      <c r="R40" s="41"/>
+      <c r="S40" s="42"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="44"/>
+      <c r="V40" s="44"/>
+      <c r="W40" s="44"/>
+      <c r="X40" s="44"/>
+      <c r="Y40" s="44"/>
+      <c r="Z40" s="44"/>
+      <c r="AA40" s="44"/>
+      <c r="AB40" s="53"/>
+      <c r="AC40" s="53"/>
+      <c r="AD40" s="42"/>
+      <c r="AE40" s="54"/>
+      <c r="AF40" s="54"/>
+      <c r="AG40" s="55"/>
+      <c r="AH40" s="55"/>
+      <c r="AI40" s="56"/>
+      <c r="AJ40" s="44"/>
+      <c r="AK40" s="57"/>
+      <c r="AL40" s="57"/>
+      <c r="AM40" s="57"/>
+      <c r="AN40" s="57"/>
+      <c r="AO40" s="57"/>
+      <c r="AP40" s="57"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="B41" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" s="43">
-        <v>-1.0</v>
-      </c>
-      <c r="D41" s="44">
-        <v>0.08</v>
-      </c>
-      <c r="E41" s="43">
-        <v>3.0</v>
-      </c>
-      <c r="F41" s="43">
-        <v>4.0</v>
-      </c>
-      <c r="G41" s="44">
-        <v>-0.2</v>
-      </c>
-      <c r="H41" s="45"/>
-      <c r="I41" s="43">
-        <v>-150.0</v>
-      </c>
-      <c r="J41" s="46"/>
-      <c r="K41" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="L41" s="48">
-        <v>3000.0</v>
-      </c>
-      <c r="M41" s="49">
-        <v>-0.018</v>
-      </c>
-      <c r="N41" s="89">
-        <v>104.0</v>
-      </c>
-      <c r="O41" s="49">
-        <v>104.0</v>
-      </c>
-      <c r="P41" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="Q41" s="49">
-        <v>0.3</v>
-      </c>
-      <c r="R41" s="49">
-        <v>0.5</v>
-      </c>
-      <c r="S41" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="T41" s="52">
-        <f>MAX(MIN($M41*Model!$A$13+$N41,$O41)*$P41,0)</f>
-        <v>103.1</v>
-      </c>
-      <c r="U41" s="52">
-        <f>MAX(MIN($M41*Model!$A$14+$N41,$O41)*$P41,0)</f>
-        <v>102.2</v>
-      </c>
-      <c r="V41" s="52">
-        <f>MAX(MIN($M41*Model!$A$15+$N41,$O41)*$P41,0)</f>
-        <v>100.4</v>
-      </c>
-      <c r="W41" s="52">
-        <f>MAX(MIN($M41*Model!$A$16+$N41,$O41)*$P41,0)</f>
-        <v>98.6</v>
-      </c>
-      <c r="X41" s="52">
-        <f>MAX(MIN($M41*Model!$A$17+$N41,$O41)*$P41,0)</f>
-        <v>96.8</v>
-      </c>
-      <c r="Y41" s="52">
-        <f>MAX(MIN($M41*Model!$A$18+$N41,$O41)*$P41,0)</f>
-        <v>94.1</v>
-      </c>
-      <c r="Z41" s="52">
-        <f>MAX(MIN($M41*Model!$A$19+$N41,$O41)*$P41,0)</f>
-        <v>90.5</v>
-      </c>
-      <c r="AA41" s="52">
-        <f>T41*Model!$B$13+U41*Model!$B$14+V41*Model!$B$15+W41*Model!$B$16+X41*Model!$B$17+Y41*Model!$B$18+Z41*Model!$B$19</f>
-        <v>98.735</v>
-      </c>
-      <c r="AB41" s="53">
-        <v>0.1</v>
-      </c>
-      <c r="AC41" s="53">
-        <v>0.9</v>
-      </c>
-      <c r="AD41" s="51" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE41,";",'7.62x54R-ammo'!$AF41,";",'7.62x54R-ammo'!$AG41,";",'7.62x54R-ammo'!$AH41,")")</f>
-        <v>stat(bullet_velocity;0.05;0.55;1500;3000)</v>
-      </c>
-      <c r="AE41" s="54">
-        <v>0.05</v>
-      </c>
-      <c r="AF41" s="54">
-        <v>0.55</v>
-      </c>
-      <c r="AG41" s="55">
-        <v>1500.0</v>
-      </c>
-      <c r="AH41" s="55">
-        <v>3000.0</v>
-      </c>
-      <c r="AI41" s="56">
-        <f>Model!$B$4+IF(I41="",0,I41)</f>
-        <v>1969</v>
-      </c>
-      <c r="AJ41" s="52">
-        <f t="shared" si="3"/>
-        <v>0.2063333333</v>
-      </c>
-      <c r="AK41" s="57">
-        <f>C41*Model!$B$24+D41*Model!$B$25+E41*Model!$B$26+F41*Model!$B$27+G41*Model!$B$28+H41*Model!$B$29+I41*Model!$B$30+J41*Model!$B$31+L41*Model!$B$32+K41*Model!$B$33</f>
-        <v>0.25</v>
-      </c>
-      <c r="AL41" s="57">
-        <f>(AA41-Model!$B$5)*Model!$B$35</f>
-        <v>-0.6325</v>
-      </c>
-      <c r="AM41" s="57">
-        <f>(Model!$B$6-AB41)*Model!$B$36</f>
-        <v>0.5</v>
-      </c>
-      <c r="AN41" s="57">
-        <f>(AC41-Model!$B$7)*Model!$B$37</f>
-        <v>0.15</v>
-      </c>
-      <c r="AO41" s="57">
-        <f>(AJ41-Model!$B$8)*Model!$B$38</f>
-        <v>-4.762</v>
-      </c>
-      <c r="AP41" s="57">
-        <f t="shared" si="4"/>
-        <v>-4.4945</v>
-      </c>
+      <c r="A41" s="88"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="38"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="66"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="40"/>
+      <c r="S41" s="42"/>
+      <c r="T41" s="44"/>
+      <c r="U41" s="44"/>
+      <c r="V41" s="44"/>
+      <c r="W41" s="44"/>
+      <c r="X41" s="44"/>
+      <c r="Y41" s="44"/>
+      <c r="Z41" s="44"/>
+      <c r="AA41" s="44"/>
+      <c r="AB41" s="53"/>
+      <c r="AC41" s="53"/>
+      <c r="AD41" s="42"/>
+      <c r="AE41" s="54"/>
+      <c r="AF41" s="54"/>
+      <c r="AG41" s="55"/>
+      <c r="AH41" s="55"/>
+      <c r="AI41" s="56"/>
+      <c r="AJ41" s="44"/>
+      <c r="AK41" s="57"/>
+      <c r="AL41" s="57"/>
+      <c r="AM41" s="57"/>
+      <c r="AN41" s="57"/>
+      <c r="AO41" s="57"/>
+      <c r="AP41" s="57"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="B42" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="C42" s="43">
-        <v>-1.0</v>
-      </c>
-      <c r="D42" s="44">
-        <v>0.03</v>
-      </c>
-      <c r="E42" s="43">
-        <v>2.0</v>
-      </c>
-      <c r="F42" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="G42" s="44">
-        <v>-0.1</v>
-      </c>
-      <c r="H42" s="45"/>
-      <c r="I42" s="43">
-        <v>0.0</v>
-      </c>
-      <c r="J42" s="46"/>
-      <c r="K42" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="L42" s="48">
-        <v>2500.0</v>
-      </c>
-      <c r="M42" s="89">
-        <v>-0.022</v>
-      </c>
-      <c r="N42" s="89">
-        <v>104.0</v>
-      </c>
-      <c r="O42" s="89">
-        <v>103.0</v>
-      </c>
-      <c r="P42" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="Q42" s="49">
-        <v>0.3</v>
-      </c>
-      <c r="R42" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="S42" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="T42" s="52">
-        <f>MAX(MIN($M42*Model!$A$13+$N42,$O42)*$P42,0)</f>
-        <v>102.9</v>
-      </c>
-      <c r="U42" s="52">
-        <f>MAX(MIN($M42*Model!$A$14+$N42,$O42)*$P42,0)</f>
-        <v>101.8</v>
-      </c>
-      <c r="V42" s="52">
-        <f>MAX(MIN($M42*Model!$A$15+$N42,$O42)*$P42,0)</f>
-        <v>99.6</v>
-      </c>
-      <c r="W42" s="52">
-        <f>MAX(MIN($M42*Model!$A$16+$N42,$O42)*$P42,0)</f>
-        <v>97.4</v>
-      </c>
-      <c r="X42" s="52">
-        <f>MAX(MIN($M42*Model!$A$17+$N42,$O42)*$P42,0)</f>
-        <v>95.2</v>
-      </c>
-      <c r="Y42" s="52">
-        <f>MAX(MIN($M42*Model!$A$18+$N42,$O42)*$P42,0)</f>
-        <v>91.9</v>
-      </c>
-      <c r="Z42" s="52">
-        <f>MAX(MIN($M42*Model!$A$19+$N42,$O42)*$P42,0)</f>
-        <v>87.5</v>
-      </c>
-      <c r="AA42" s="52">
-        <f>T42*Model!$B$13+U42*Model!$B$14+V42*Model!$B$15+W42*Model!$B$16+X42*Model!$B$17+Y42*Model!$B$18+Z42*Model!$B$19</f>
-        <v>97.565</v>
-      </c>
-      <c r="AB42" s="53">
-        <v>0.15</v>
-      </c>
-      <c r="AC42" s="53">
-        <v>1.0</v>
-      </c>
-      <c r="AD42" s="51" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE42,";",'7.62x54R-ammo'!$AF42,";",'7.62x54R-ammo'!$AG42,";",'7.62x54R-ammo'!$AH42,")")</f>
-        <v>stat(bullet_velocity;1.1;1.6;1500;3000)</v>
-      </c>
-      <c r="AE42" s="54">
-        <v>1.1</v>
-      </c>
-      <c r="AF42" s="54">
-        <v>1.6</v>
-      </c>
-      <c r="AG42" s="55">
-        <v>1500.0</v>
-      </c>
-      <c r="AH42" s="55">
-        <v>3000.0</v>
-      </c>
-      <c r="AI42" s="56">
-        <f>Model!$B$4+IF(I42="",0,I42)</f>
-        <v>2119</v>
-      </c>
-      <c r="AJ42" s="52">
-        <f t="shared" si="3"/>
-        <v>1.306333333</v>
-      </c>
-      <c r="AK42" s="57">
-        <f>C42*Model!$B$24+D42*Model!$B$25+E42*Model!$B$26+F42*Model!$B$27+G42*Model!$B$28+H42*Model!$B$29+I42*Model!$B$30+J42*Model!$B$31+L42*Model!$B$32+K42*Model!$B$33</f>
-        <v>0.3</v>
-      </c>
-      <c r="AL42" s="57">
-        <f>(AA42-Model!$B$5)*Model!$B$35</f>
-        <v>-1.2175</v>
-      </c>
-      <c r="AM42" s="57">
-        <f>(Model!$B$6-AB42)*Model!$B$36</f>
-        <v>0.4</v>
-      </c>
-      <c r="AN42" s="57">
-        <f>(AC42-Model!$B$7)*Model!$B$37</f>
-        <v>0.45</v>
-      </c>
-      <c r="AO42" s="57">
-        <f>(AJ42-Model!$B$8)*Model!$B$38</f>
-        <v>1.838</v>
-      </c>
-      <c r="AP42" s="57">
-        <f t="shared" si="4"/>
-        <v>1.7705</v>
-      </c>
+      <c r="A42" s="88"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="38"/>
+      <c r="M42" s="66"/>
+      <c r="N42" s="66"/>
+      <c r="O42" s="66"/>
+      <c r="P42" s="40"/>
+      <c r="Q42" s="40"/>
+      <c r="R42" s="41"/>
+      <c r="S42" s="42"/>
+      <c r="T42" s="44"/>
+      <c r="U42" s="44"/>
+      <c r="V42" s="44"/>
+      <c r="W42" s="44"/>
+      <c r="X42" s="44"/>
+      <c r="Y42" s="44"/>
+      <c r="Z42" s="44"/>
+      <c r="AA42" s="44"/>
+      <c r="AB42" s="53"/>
+      <c r="AC42" s="53"/>
+      <c r="AD42" s="42"/>
+      <c r="AE42" s="54"/>
+      <c r="AF42" s="54"/>
+      <c r="AG42" s="55"/>
+      <c r="AH42" s="55"/>
+      <c r="AI42" s="56"/>
+      <c r="AJ42" s="44"/>
+      <c r="AK42" s="57"/>
+      <c r="AL42" s="57"/>
+      <c r="AM42" s="57"/>
+      <c r="AN42" s="57"/>
+      <c r="AO42" s="57"/>
+      <c r="AP42" s="57"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="B43" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C43" s="43">
-        <v>-1.0</v>
-      </c>
-      <c r="D43" s="44">
-        <v>-0.04</v>
-      </c>
-      <c r="E43" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="F43" s="43">
-        <v>2.0</v>
-      </c>
-      <c r="G43" s="44">
-        <v>-0.1</v>
-      </c>
-      <c r="H43" s="45"/>
-      <c r="I43" s="43">
-        <v>150.0</v>
-      </c>
-      <c r="J43" s="46"/>
-      <c r="K43" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="L43" s="48">
-        <v>2500.0</v>
-      </c>
-      <c r="M43" s="89">
-        <v>-0.024</v>
-      </c>
-      <c r="N43" s="89">
-        <v>104.5</v>
-      </c>
-      <c r="O43" s="89">
-        <v>104.0</v>
-      </c>
-      <c r="P43" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="Q43" s="89">
-        <v>0.3</v>
-      </c>
-      <c r="R43" s="89">
-        <v>0.5</v>
-      </c>
-      <c r="S43" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="T43" s="52">
-        <f>MAX(MIN($M43*Model!$A$13+$N43,$O43)*$P43,0)</f>
-        <v>103.3</v>
-      </c>
-      <c r="U43" s="52">
-        <f>MAX(MIN($M43*Model!$A$14+$N43,$O43)*$P43,0)</f>
-        <v>102.1</v>
-      </c>
-      <c r="V43" s="52">
-        <f>MAX(MIN($M43*Model!$A$15+$N43,$O43)*$P43,0)</f>
-        <v>99.7</v>
-      </c>
-      <c r="W43" s="52">
-        <f>MAX(MIN($M43*Model!$A$16+$N43,$O43)*$P43,0)</f>
-        <v>97.3</v>
-      </c>
-      <c r="X43" s="52">
-        <f>MAX(MIN($M43*Model!$A$17+$N43,$O43)*$P43,0)</f>
-        <v>94.9</v>
-      </c>
-      <c r="Y43" s="52">
-        <f>MAX(MIN($M43*Model!$A$18+$N43,$O43)*$P43,0)</f>
-        <v>91.3</v>
-      </c>
-      <c r="Z43" s="52">
-        <f>MAX(MIN($M43*Model!$A$19+$N43,$O43)*$P43,0)</f>
-        <v>86.5</v>
-      </c>
-      <c r="AA43" s="52">
-        <f>T43*Model!$B$13+U43*Model!$B$14+V43*Model!$B$15+W43*Model!$B$16+X43*Model!$B$17+Y43*Model!$B$18+Z43*Model!$B$19</f>
-        <v>97.48</v>
-      </c>
-      <c r="AB43" s="53">
-        <v>0.2</v>
-      </c>
-      <c r="AC43" s="53">
-        <v>0.9</v>
-      </c>
-      <c r="AD43" s="51" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE43,";",'7.62x54R-ammo'!$AF43,";",'7.62x54R-ammo'!$AG43,";",'7.62x54R-ammo'!$AH43,")")</f>
-        <v>stat(bullet_velocity;0.85;1.35;1500;3000)</v>
-      </c>
-      <c r="AE43" s="54">
-        <v>0.85</v>
-      </c>
-      <c r="AF43" s="54">
-        <v>1.35</v>
-      </c>
-      <c r="AG43" s="55">
-        <v>1500.0</v>
-      </c>
-      <c r="AH43" s="55">
-        <v>3000.0</v>
-      </c>
-      <c r="AI43" s="56">
-        <f>Model!$B$4+IF(I43="",0,I43)</f>
-        <v>2269</v>
-      </c>
-      <c r="AJ43" s="52">
-        <f t="shared" si="3"/>
-        <v>1.106333333</v>
-      </c>
-      <c r="AK43" s="57">
-        <f>C43*Model!$B$24+D43*Model!$B$25+E43*Model!$B$26+F43*Model!$B$27+G43*Model!$B$28+H43*Model!$B$29+I43*Model!$B$30+J43*Model!$B$31+L43*Model!$B$32+K43*Model!$B$33</f>
-        <v>2.55</v>
-      </c>
-      <c r="AL43" s="57">
-        <f>(AA43-Model!$B$5)*Model!$B$35</f>
-        <v>-1.26</v>
-      </c>
-      <c r="AM43" s="57">
-        <f>(Model!$B$6-AB43)*Model!$B$36</f>
-        <v>0.3</v>
-      </c>
-      <c r="AN43" s="57">
-        <f>(AC43-Model!$B$7)*Model!$B$37</f>
-        <v>0.15</v>
-      </c>
-      <c r="AO43" s="57">
-        <f>(AJ43-Model!$B$8)*Model!$B$38</f>
-        <v>0.638</v>
-      </c>
-      <c r="AP43" s="57">
-        <f t="shared" si="4"/>
-        <v>2.378</v>
-      </c>
+      <c r="A43" s="88"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="36"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="66"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="40"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="66"/>
+      <c r="S43" s="42"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="44"/>
+      <c r="V43" s="44"/>
+      <c r="W43" s="44"/>
+      <c r="X43" s="44"/>
+      <c r="Y43" s="44"/>
+      <c r="Z43" s="44"/>
+      <c r="AA43" s="44"/>
+      <c r="AB43" s="53"/>
+      <c r="AC43" s="53"/>
+      <c r="AD43" s="42"/>
+      <c r="AE43" s="54"/>
+      <c r="AF43" s="54"/>
+      <c r="AG43" s="55"/>
+      <c r="AH43" s="55"/>
+      <c r="AI43" s="56"/>
+      <c r="AJ43" s="44"/>
+      <c r="AK43" s="57"/>
+      <c r="AL43" s="57"/>
+      <c r="AM43" s="57"/>
+      <c r="AN43" s="57"/>
+      <c r="AO43" s="57"/>
+      <c r="AP43" s="57"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="58" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" s="43">
-        <v>-1.0</v>
-      </c>
-      <c r="D44" s="44">
-        <v>-0.06</v>
-      </c>
-      <c r="E44" s="43">
-        <v>2.0</v>
-      </c>
-      <c r="F44" s="43">
-        <v>3.0</v>
-      </c>
-      <c r="G44" s="44">
-        <v>-0.05</v>
-      </c>
-      <c r="H44" s="60"/>
-      <c r="I44" s="43">
-        <v>150.0</v>
-      </c>
-      <c r="J44" s="61"/>
-      <c r="K44" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="L44" s="48">
-        <v>4000.0</v>
-      </c>
-      <c r="M44" s="49">
-        <v>-0.02</v>
-      </c>
-      <c r="N44" s="89">
-        <v>103.0</v>
-      </c>
-      <c r="O44" s="89">
-        <v>102.0</v>
-      </c>
-      <c r="P44" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="Q44" s="89">
-        <v>0.25</v>
-      </c>
-      <c r="R44" s="89">
-        <v>0.45</v>
-      </c>
-      <c r="S44" s="62">
-        <v>2.5</v>
-      </c>
-      <c r="T44" s="63">
-        <f>MAX(MIN($M44*Model!$A$13+$N44,$O44)*$P44,0)</f>
-        <v>102</v>
-      </c>
-      <c r="U44" s="63">
-        <f>MAX(MIN($M44*Model!$A$14+$N44,$O44)*$P44,0)</f>
-        <v>101</v>
-      </c>
-      <c r="V44" s="63">
-        <f>MAX(MIN($M44*Model!$A$15+$N44,$O44)*$P44,0)</f>
-        <v>99</v>
-      </c>
-      <c r="W44" s="63">
-        <f>MAX(MIN($M44*Model!$A$16+$N44,$O44)*$P44,0)</f>
-        <v>97</v>
-      </c>
-      <c r="X44" s="63">
-        <f>MAX(MIN($M44*Model!$A$17+$N44,$O44)*$P44,0)</f>
-        <v>95</v>
-      </c>
-      <c r="Y44" s="63">
-        <f>MAX(MIN($M44*Model!$A$18+$N44,$O44)*$P44,0)</f>
-        <v>92</v>
-      </c>
-      <c r="Z44" s="63">
-        <f>MAX(MIN($M44*Model!$A$19+$N44,$O44)*$P44,0)</f>
-        <v>88</v>
-      </c>
-      <c r="AA44" s="63">
-        <f>T44*Model!$B$13+U44*Model!$B$14+V44*Model!$B$15+W44*Model!$B$16+X44*Model!$B$17+Y44*Model!$B$18+Z44*Model!$B$19</f>
-        <v>97.15</v>
-      </c>
-      <c r="AB44" s="53">
-        <v>0.15</v>
-      </c>
-      <c r="AC44" s="53">
-        <v>1.0</v>
-      </c>
-      <c r="AD44" s="62" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE44,";",'7.62x54R-ammo'!$AF44,";",'7.62x54R-ammo'!$AG44,";",'7.62x54R-ammo'!$AH44,")")</f>
-        <v>stat(bullet_velocity;1.5;2;1500;3000)</v>
-      </c>
-      <c r="AE44" s="54">
-        <v>1.5</v>
-      </c>
-      <c r="AF44" s="54">
-        <v>2.0</v>
-      </c>
-      <c r="AG44" s="64">
-        <v>1500.0</v>
-      </c>
-      <c r="AH44" s="64">
-        <v>3000.0</v>
-      </c>
-      <c r="AI44" s="65">
-        <f>Model!$B$4+IF(I44="",0,I44)</f>
-        <v>2269</v>
-      </c>
-      <c r="AJ44" s="63">
-        <f t="shared" si="3"/>
-        <v>1.756333333</v>
-      </c>
-      <c r="AK44" s="57">
-        <f>C44*Model!$B$24+D44*Model!$B$25+E44*Model!$B$26+F44*Model!$B$27+G44*Model!$B$28+H44*Model!$B$29+I44*Model!$B$30+J44*Model!$B$31+L44*Model!$B$32+K44*Model!$B$33</f>
-        <v>0.75</v>
-      </c>
-      <c r="AL44" s="66">
-        <f>(AA44-Model!$B$5)*Model!$B$35</f>
-        <v>-1.425</v>
-      </c>
-      <c r="AM44" s="66">
-        <f>(Model!$B$6-AB44)*Model!$B$36</f>
-        <v>0.4</v>
-      </c>
-      <c r="AN44" s="66">
-        <f>(AC44-Model!$B$7)*Model!$B$37</f>
-        <v>0.45</v>
-      </c>
-      <c r="AO44" s="66">
-        <f>(AJ44-Model!$B$8)*Model!$B$38</f>
-        <v>4.538</v>
-      </c>
-      <c r="AP44" s="66">
-        <f t="shared" si="4"/>
-        <v>4.713</v>
-      </c>
+      <c r="A44" s="88"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="60"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="40"/>
+      <c r="N44" s="66"/>
+      <c r="O44" s="66"/>
+      <c r="P44" s="40"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="66"/>
+      <c r="S44" s="61"/>
+      <c r="T44" s="62"/>
+      <c r="U44" s="62"/>
+      <c r="V44" s="62"/>
+      <c r="W44" s="62"/>
+      <c r="X44" s="62"/>
+      <c r="Y44" s="62"/>
+      <c r="Z44" s="62"/>
+      <c r="AA44" s="62"/>
+      <c r="AB44" s="53"/>
+      <c r="AC44" s="53"/>
+      <c r="AD44" s="61"/>
+      <c r="AE44" s="54"/>
+      <c r="AF44" s="54"/>
+      <c r="AG44" s="63"/>
+      <c r="AH44" s="63"/>
+      <c r="AI44" s="64"/>
+      <c r="AJ44" s="62"/>
+      <c r="AK44" s="57"/>
+      <c r="AL44" s="65"/>
+      <c r="AM44" s="65"/>
+      <c r="AN44" s="65"/>
+      <c r="AO44" s="65"/>
+      <c r="AP44" s="65"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="88" t="s">
-        <v>116</v>
-      </c>
-      <c r="B45" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="C45" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="D45" s="44">
-        <v>-0.05</v>
-      </c>
-      <c r="E45" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="F45" s="43">
-        <v>2.0</v>
-      </c>
-      <c r="G45" s="44">
-        <v>-0.05</v>
-      </c>
-      <c r="H45" s="45"/>
-      <c r="I45" s="43">
-        <v>200.0</v>
-      </c>
-      <c r="J45" s="46"/>
-      <c r="K45" s="47">
-        <v>0.0</v>
-      </c>
-      <c r="L45" s="48">
-        <v>3500.0</v>
-      </c>
-      <c r="M45" s="89">
-        <v>-0.032</v>
-      </c>
-      <c r="N45" s="89">
-        <v>106.5</v>
-      </c>
-      <c r="O45" s="89">
-        <v>106.0</v>
-      </c>
-      <c r="P45" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="Q45" s="89">
-        <v>0.3</v>
-      </c>
-      <c r="R45" s="89">
-        <v>0.5</v>
-      </c>
-      <c r="S45" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="T45" s="52">
-        <f>MAX(MIN($M45*Model!$A$13+$N45,$O45)*$P45,0)</f>
-        <v>104.9</v>
-      </c>
-      <c r="U45" s="52">
-        <f>MAX(MIN($M45*Model!$A$14+$N45,$O45)*$P45,0)</f>
-        <v>103.3</v>
-      </c>
-      <c r="V45" s="52">
-        <f>MAX(MIN($M45*Model!$A$15+$N45,$O45)*$P45,0)</f>
-        <v>100.1</v>
-      </c>
-      <c r="W45" s="52">
-        <f>MAX(MIN($M45*Model!$A$16+$N45,$O45)*$P45,0)</f>
-        <v>96.9</v>
-      </c>
-      <c r="X45" s="52">
-        <f>MAX(MIN($M45*Model!$A$17+$N45,$O45)*$P45,0)</f>
-        <v>93.7</v>
-      </c>
-      <c r="Y45" s="52">
-        <f>MAX(MIN($M45*Model!$A$18+$N45,$O45)*$P45,0)</f>
-        <v>88.9</v>
-      </c>
-      <c r="Z45" s="52">
-        <f>MAX(MIN($M45*Model!$A$19+$N45,$O45)*$P45,0)</f>
-        <v>82.5</v>
-      </c>
-      <c r="AA45" s="52">
-        <f>T45*Model!$B$13+U45*Model!$B$14+V45*Model!$B$15+W45*Model!$B$16+X45*Model!$B$17+Y45*Model!$B$18+Z45*Model!$B$19</f>
-        <v>97.14</v>
-      </c>
-      <c r="AB45" s="53">
-        <v>0.3</v>
-      </c>
-      <c r="AC45" s="53">
-        <v>0.8</v>
-      </c>
-      <c r="AD45" s="51" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE45,";",'7.62x54R-ammo'!$AF45,";",'7.62x54R-ammo'!$AG45,";",'7.62x54R-ammo'!$AH45,")")</f>
-        <v>stat(bullet_velocity;0.35;0.85;1500;3000)</v>
-      </c>
-      <c r="AE45" s="54">
-        <v>0.35</v>
-      </c>
-      <c r="AF45" s="54">
-        <v>0.85</v>
-      </c>
-      <c r="AG45" s="55">
-        <v>1500.0</v>
-      </c>
-      <c r="AH45" s="55">
-        <v>3000.0</v>
-      </c>
-      <c r="AI45" s="56">
-        <f>Model!$B$4+IF(I45="",0,I45)</f>
-        <v>2319</v>
-      </c>
-      <c r="AJ45" s="52">
-        <f t="shared" si="3"/>
-        <v>0.623</v>
-      </c>
-      <c r="AK45" s="57">
-        <f>C45*Model!$B$24+D45*Model!$B$25+E45*Model!$B$26+F45*Model!$B$27+G45*Model!$B$28+H45*Model!$B$29+I45*Model!$B$30+J45*Model!$B$31+L45*Model!$B$32+K45*Model!$B$33</f>
-        <v>3.5</v>
-      </c>
-      <c r="AL45" s="57">
-        <f>(AA45-Model!$B$5)*Model!$B$35</f>
-        <v>-1.43</v>
-      </c>
-      <c r="AM45" s="57">
-        <f>(Model!$B$6-AB45)*Model!$B$36</f>
-        <v>0.1</v>
-      </c>
-      <c r="AN45" s="57">
-        <f>(AC45-Model!$B$7)*Model!$B$37</f>
-        <v>-0.15</v>
-      </c>
-      <c r="AO45" s="57">
-        <f>(AJ45-Model!$B$8)*Model!$B$38</f>
-        <v>-2.262</v>
-      </c>
-      <c r="AP45" s="57">
-        <f t="shared" si="4"/>
-        <v>-0.242</v>
-      </c>
+      <c r="A45" s="30"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="38"/>
+      <c r="M45" s="66"/>
+      <c r="N45" s="66"/>
+      <c r="O45" s="66"/>
+      <c r="P45" s="40"/>
+      <c r="Q45" s="66"/>
+      <c r="R45" s="66"/>
+      <c r="S45" s="42"/>
+      <c r="T45" s="44"/>
+      <c r="U45" s="44"/>
+      <c r="V45" s="44"/>
+      <c r="W45" s="44"/>
+      <c r="X45" s="44"/>
+      <c r="Y45" s="44"/>
+      <c r="Z45" s="44"/>
+      <c r="AA45" s="44"/>
+      <c r="AB45" s="53"/>
+      <c r="AC45" s="53"/>
+      <c r="AD45" s="42"/>
+      <c r="AE45" s="54"/>
+      <c r="AF45" s="54"/>
+      <c r="AG45" s="55"/>
+      <c r="AH45" s="55"/>
+      <c r="AI45" s="56"/>
+      <c r="AJ45" s="44"/>
+      <c r="AK45" s="57"/>
+      <c r="AL45" s="57"/>
+      <c r="AM45" s="57"/>
+      <c r="AN45" s="57"/>
+      <c r="AO45" s="57"/>
+      <c r="AP45" s="57"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="B46" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="C46" s="43">
-        <v>3.0</v>
-      </c>
-      <c r="D46" s="44">
-        <v>0.11</v>
-      </c>
-      <c r="E46" s="43">
-        <v>-3.0</v>
-      </c>
-      <c r="F46" s="43">
-        <v>-3.0</v>
-      </c>
-      <c r="G46" s="44">
-        <v>0.2</v>
-      </c>
-      <c r="H46" s="45"/>
-      <c r="I46" s="43">
-        <v>-900.0</v>
-      </c>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47">
-        <v>-0.3</v>
-      </c>
-      <c r="L46" s="48">
-        <v>2500.0</v>
-      </c>
-      <c r="M46" s="89">
-        <v>-0.064</v>
-      </c>
-      <c r="N46" s="89">
-        <v>109.5</v>
-      </c>
-      <c r="O46" s="89">
-        <v>109.5</v>
-      </c>
-      <c r="P46" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="Q46" s="49">
-        <v>0.3</v>
-      </c>
-      <c r="R46" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="S46" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="T46" s="52">
-        <f>MAX(MIN($M46*Model!$A$13+$N46,$O46)*$P46,0)</f>
-        <v>106.3</v>
-      </c>
-      <c r="U46" s="52">
-        <f>MAX(MIN($M46*Model!$A$14+$N46,$O46)*$P46,0)</f>
-        <v>103.1</v>
-      </c>
-      <c r="V46" s="52">
-        <f>MAX(MIN($M46*Model!$A$15+$N46,$O46)*$P46,0)</f>
-        <v>96.7</v>
-      </c>
-      <c r="W46" s="52">
-        <f>MAX(MIN($M46*Model!$A$16+$N46,$O46)*$P46,0)</f>
-        <v>90.3</v>
-      </c>
-      <c r="X46" s="52">
-        <f>MAX(MIN($M46*Model!$A$17+$N46,$O46)*$P46,0)</f>
-        <v>83.9</v>
-      </c>
-      <c r="Y46" s="52">
-        <f>MAX(MIN($M46*Model!$A$18+$N46,$O46)*$P46,0)</f>
-        <v>74.3</v>
-      </c>
-      <c r="Z46" s="52">
-        <f>MAX(MIN($M46*Model!$A$19+$N46,$O46)*$P46,0)</f>
-        <v>61.5</v>
-      </c>
-      <c r="AA46" s="52">
-        <f>T46*Model!$B$13+U46*Model!$B$14+V46*Model!$B$15+W46*Model!$B$16+X46*Model!$B$17+Y46*Model!$B$18+Z46*Model!$B$19</f>
-        <v>90.78</v>
-      </c>
-      <c r="AB46" s="53">
-        <v>0.7</v>
-      </c>
-      <c r="AC46" s="53">
-        <v>0.2</v>
-      </c>
-      <c r="AD46" s="51" t="str">
-        <f>CONCATENATE("stat(bullet_velocity;",'7.62x54R-ammo'!$AE46,";",'7.62x54R-ammo'!$AF46,";",'7.62x54R-ammo'!$AG46,";",'7.62x54R-ammo'!$AH46,")")</f>
-        <v>stat(bullet_velocity;0.2;0.7;1500;3000)</v>
-      </c>
-      <c r="AE46" s="54">
-        <v>0.2</v>
-      </c>
-      <c r="AF46" s="54">
-        <v>0.7</v>
-      </c>
-      <c r="AG46" s="55">
-        <v>1500.0</v>
-      </c>
-      <c r="AH46" s="55">
-        <v>3000.0</v>
-      </c>
-      <c r="AI46" s="56">
-        <f>Model!$B$4+IF(I46="",0,I46)</f>
-        <v>1219</v>
-      </c>
-      <c r="AJ46" s="52">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="AK46" s="57">
-        <f>C46*Model!$B$24+D46*Model!$B$25+E46*Model!$B$26+F46*Model!$B$27+G46*Model!$B$28+H46*Model!$B$29+I46*Model!$B$30+J46*Model!$B$31+L46*Model!$B$32+K46*Model!$B$33</f>
-        <v>-4.6</v>
-      </c>
-      <c r="AL46" s="57">
-        <f>(AA46-Model!$B$5)*Model!$B$35</f>
-        <v>-4.61</v>
-      </c>
-      <c r="AM46" s="57">
-        <f>(Model!$B$6-AB46)*Model!$B$36</f>
-        <v>-0.7</v>
-      </c>
-      <c r="AN46" s="57">
-        <f>(AC46-Model!$B$7)*Model!$B$37</f>
-        <v>-1.95</v>
-      </c>
-      <c r="AO46" s="57">
-        <f>(AJ46-Model!$B$8)*Model!$B$38</f>
-        <v>-4.8</v>
-      </c>
-      <c r="AP46" s="57">
-        <f t="shared" si="4"/>
-        <v>-16.66</v>
-      </c>
+      <c r="A46" s="88"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="38"/>
+      <c r="M46" s="66"/>
+      <c r="N46" s="66"/>
+      <c r="O46" s="66"/>
+      <c r="P46" s="40"/>
+      <c r="Q46" s="40"/>
+      <c r="R46" s="41"/>
+      <c r="S46" s="42"/>
+      <c r="T46" s="44"/>
+      <c r="U46" s="44"/>
+      <c r="V46" s="44"/>
+      <c r="W46" s="44"/>
+      <c r="X46" s="44"/>
+      <c r="Y46" s="44"/>
+      <c r="Z46" s="44"/>
+      <c r="AA46" s="44"/>
+      <c r="AB46" s="53"/>
+      <c r="AC46" s="53"/>
+      <c r="AD46" s="42"/>
+      <c r="AE46" s="54"/>
+      <c r="AF46" s="54"/>
+      <c r="AG46" s="55"/>
+      <c r="AH46" s="55"/>
+      <c r="AI46" s="56"/>
+      <c r="AJ46" s="44"/>
+      <c r="AK46" s="57"/>
+      <c r="AL46" s="57"/>
+      <c r="AM46" s="57"/>
+      <c r="AN46" s="57"/>
+      <c r="AO46" s="57"/>
+      <c r="AP46" s="57"/>
     </row>
     <row r="47" ht="14.25" customHeight="1"/>
     <row r="48" ht="14.25" customHeight="1"/>
@@ -5501,362 +4515,362 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
+        <v>5</v>
+      </c>
+      <c r="B4" s="8">
         <v>2119.0</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>5</v>
+      <c r="C4" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="10">
+      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="11">
         <v>100.0</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>7</v>
+      <c r="C5" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="11">
+      <c r="A6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="12">
         <v>0.35</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>9</v>
+      <c r="C6" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="11">
+      <c r="A7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="12">
         <v>0.85</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>11</v>
+      <c r="C7" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="11">
+      <c r="A8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12">
         <v>1.0</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>11</v>
+      <c r="C8" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
+      <c r="A10" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>16</v>
+      <c r="A12" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="17">
+      <c r="A13" s="22">
         <v>50.0</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="23">
         <v>0.1</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>17</v>
+      <c r="C13" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="17">
+      <c r="A14" s="22">
         <v>100.0</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="23">
         <v>0.15</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>17</v>
+      <c r="C14" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="17">
+      <c r="A15" s="22">
         <v>200.0</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="26">
         <v>0.2</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>18</v>
+      <c r="C15" s="25" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="17">
+      <c r="A16" s="22">
         <v>300.0</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="26">
         <v>0.2</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>19</v>
+      <c r="C16" s="25" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="17">
+      <c r="A17" s="22">
         <v>400.0</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="26">
         <v>0.2</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>20</v>
+      <c r="C17" s="25" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="17">
+      <c r="A18" s="22">
         <v>550.0</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="23">
         <v>0.1</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>21</v>
+      <c r="C18" s="25" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="17">
+      <c r="A19" s="22">
         <v>750.0</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="23">
         <v>0.05</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>22</v>
+      <c r="C19" s="25" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="20">
+      <c r="A20" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="26">
         <f>SUM(B13:B19)</f>
         <v>1</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="29"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
+      <c r="A22" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>27</v>
+      <c r="A23" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="23">
+      <c r="A24" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="34">
         <v>1.0</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="34">
+        <v>-20.0</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="23">
-        <v>-20.0</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="24">
+      <c r="A26" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="39">
         <v>-0.4</v>
       </c>
-      <c r="C26" s="19" t="s">
-        <v>9</v>
+      <c r="C26" s="25" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="24">
+      <c r="A27" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="39">
         <v>-0.3</v>
       </c>
-      <c r="C27" s="19" t="s">
-        <v>9</v>
+      <c r="C27" s="25" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="24">
+      <c r="A28" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="39">
         <v>-30.0</v>
       </c>
-      <c r="C28" s="19" t="s">
-        <v>9</v>
+      <c r="C28" s="25" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="23">
+      <c r="A29" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="34">
         <v>10.0</v>
       </c>
-      <c r="C29" s="19" t="s">
-        <v>35</v>
+      <c r="C29" s="25" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="26">
+      <c r="A30" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="43">
         <v>0.005</v>
       </c>
-      <c r="C30" s="19" t="str">
+      <c r="C30" s="25" t="str">
         <f>CONCAT("1 point per +", 1/B30)</f>
         <v>1 point per +200</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="23">
+      <c r="A31" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="34">
         <v>10.0</v>
       </c>
-      <c r="C31" s="19" t="s">
-        <v>35</v>
+      <c r="C31" s="25" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="23">
+      <c r="A32" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="34">
         <v>0.0</v>
       </c>
-      <c r="C32" s="19" t="s">
-        <v>40</v>
+      <c r="C32" s="25" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="30">
+      <c r="A33" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="46">
         <v>-10.0</v>
       </c>
-      <c r="C33" s="29" t="s">
-        <v>43</v>
+      <c r="C33" s="45" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15"/>
+      <c r="A34" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="18"/>
+      <c r="C34" s="19"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="33">
+      <c r="A35" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="48">
         <v>0.5</v>
       </c>
-      <c r="C35" s="31" t="s">
-        <v>47</v>
+      <c r="C35" s="47" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="34">
+      <c r="A36" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="49">
         <v>2.0</v>
       </c>
-      <c r="C36" s="31" t="s">
-        <v>50</v>
+      <c r="C36" s="47" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="34">
+      <c r="A37" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="49">
         <v>3.0</v>
       </c>
-      <c r="C37" s="31" t="s">
-        <v>52</v>
+      <c r="C37" s="47" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="B38" s="37">
+      <c r="A38" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="51">
         <v>6.0</v>
       </c>
-      <c r="C38" s="38" t="s">
-        <v>54</v>
+      <c r="C38" s="52" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1"/>
